--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75DD9270-A85D-4476-9539-A796C2FBCEA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A14F47C-278C-4973-AEF6-1596F88025DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -263,13 +263,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B9">
-            <v>150320.02510286708</v>
+            <v>148111.95033115722</v>
           </cell>
           <cell r="C9">
             <v>13781.46783678359</v>
           </cell>
           <cell r="D9">
-            <v>10.907403107066262</v>
+            <v>10.747182526946604</v>
           </cell>
         </row>
         <row r="10">
@@ -277,13 +277,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B10">
-            <v>295894.57453017333</v>
+            <v>319614.24010068353</v>
           </cell>
           <cell r="C10">
             <v>3833.3433721023121</v>
           </cell>
           <cell r="D10">
-            <v>77.18968686280158</v>
+            <v>83.377409502816903</v>
           </cell>
         </row>
         <row r="12">
@@ -310,13 +310,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B14">
-            <v>119904.35650000001</v>
+            <v>120104.39150000001</v>
           </cell>
           <cell r="C14">
             <v>344799.25199999998</v>
           </cell>
           <cell r="D14">
-            <v>0.34775120828858413</v>
+            <v>0.34833135745897736</v>
           </cell>
         </row>
         <row r="15">
@@ -324,13 +324,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B15">
-            <v>81503.28</v>
+            <v>104004.71860786516</v>
           </cell>
           <cell r="C15">
             <v>108924.24443806437</v>
           </cell>
           <cell r="D15">
-            <v>0.74825655592537743</v>
+            <v>0.95483534583527441</v>
           </cell>
         </row>
         <row r="17">
@@ -401,13 +401,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B24">
-            <v>150320.02510286708</v>
+            <v>148111.95033115722</v>
           </cell>
           <cell r="C24">
-            <v>446214.59963304037</v>
+            <v>467726.19043184072</v>
           </cell>
           <cell r="D24">
-            <v>0.33687832093904552</v>
+            <v>0.3166637946752755</v>
           </cell>
         </row>
         <row r="25">
@@ -415,10 +415,10 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B25">
-            <v>295894.57453017333</v>
+            <v>319614.24010068353</v>
           </cell>
           <cell r="D25">
-            <v>0.66312167906095454</v>
+            <v>0.68333620532472461</v>
           </cell>
         </row>
         <row r="27">
@@ -445,13 +445,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B29">
-            <v>10.907403107066262</v>
+            <v>10.747182526946604</v>
           </cell>
           <cell r="C29">
             <v>10</v>
           </cell>
           <cell r="D29">
-            <v>0.90740310706626204</v>
+            <v>0.74718252694660414</v>
           </cell>
         </row>
         <row r="30">
@@ -459,13 +459,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B30">
-            <v>77.18968686280158</v>
+            <v>83.377409502816903</v>
           </cell>
           <cell r="C30">
             <v>15</v>
           </cell>
           <cell r="D30">
-            <v>62.18968686280158</v>
+            <v>68.377409502816903</v>
           </cell>
         </row>
         <row r="32">
@@ -492,13 +492,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B34">
-            <v>150320.02510286708</v>
+            <v>148111.95033115722</v>
           </cell>
           <cell r="C34">
-            <v>119904.35650000001</v>
+            <v>120104.39150000001</v>
           </cell>
           <cell r="D34">
-            <v>123942.66483131783</v>
+            <v>127098.87498460655</v>
           </cell>
         </row>
         <row r="35">
@@ -506,13 +506,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B35">
-            <v>295894.57453017333</v>
+            <v>319614.24010068353</v>
           </cell>
           <cell r="C35">
-            <v>81503.28</v>
+            <v>104004.71860786516</v>
           </cell>
           <cell r="D35">
-            <v>60700.217828077599</v>
+            <v>64228.094068532191</v>
           </cell>
         </row>
       </sheetData>
@@ -952,7 +952,7 @@
       </c>
       <c r="B9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B9</f>
-        <v>150320.02510286708</v>
+        <v>148111.95033115722</v>
       </c>
       <c r="C9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C9</f>
@@ -960,7 +960,7 @@
       </c>
       <c r="D9" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D9</f>
-        <v>10.907403107066262</v>
+        <v>10.747182526946604</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -970,7 +970,7 @@
       </c>
       <c r="B10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B10</f>
-        <v>295894.57453017333</v>
+        <v>319614.24010068353</v>
       </c>
       <c r="C10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C10</f>
@@ -978,7 +978,7 @@
       </c>
       <c r="D10" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D10</f>
-        <v>77.18968686280158</v>
+        <v>83.377409502816903</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B14</f>
-        <v>119904.35650000001</v>
+        <v>120104.39150000001</v>
       </c>
       <c r="C14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C14</f>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="D14" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D14</f>
-        <v>0.34775120828858413</v>
+        <v>0.34833135745897736</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B15" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B15</f>
-        <v>81503.28</v>
+        <v>104004.71860786516</v>
       </c>
       <c r="C15" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C15</f>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="D15" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D15</f>
-        <v>0.74825655592537743</v>
+        <v>0.95483534583527441</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1138,15 +1138,15 @@
       </c>
       <c r="B24" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B24</f>
-        <v>150320.02510286708</v>
+        <v>148111.95033115722</v>
       </c>
       <c r="C24" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C24</f>
-        <v>446214.59963304037</v>
+        <v>467726.19043184072</v>
       </c>
       <c r="D24" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D24</f>
-        <v>0.33687832093904552</v>
+        <v>0.3166637946752755</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B25" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B25</f>
-        <v>295894.57453017333</v>
+        <v>319614.24010068353</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D25</f>
-        <v>0.66312167906095454</v>
+        <v>0.68333620532472461</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B29" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B29</f>
-        <v>10.907403107066262</v>
+        <v>10.747182526946604</v>
       </c>
       <c r="C29" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C29</f>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="D29" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D29</f>
-        <v>0.90740310706626204</v>
+        <v>0.74718252694660414</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B30" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B30</f>
-        <v>77.18968686280158</v>
+        <v>83.377409502816903</v>
       </c>
       <c r="C30" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C30</f>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="D30" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D30</f>
-        <v>62.18968686280158</v>
+        <v>68.377409502816903</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1261,15 +1261,15 @@
       </c>
       <c r="B34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B34</f>
-        <v>150320.02510286708</v>
+        <v>148111.95033115722</v>
       </c>
       <c r="C34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C34</f>
-        <v>119904.35650000001</v>
+        <v>120104.39150000001</v>
       </c>
       <c r="D34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D34</f>
-        <v>123942.66483131783</v>
+        <v>127098.87498460655</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1279,15 +1279,15 @@
       </c>
       <c r="B35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B35</f>
-        <v>295894.57453017333</v>
+        <v>319614.24010068353</v>
       </c>
       <c r="C35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C35</f>
-        <v>81503.28</v>
+        <v>104004.71860786516</v>
       </c>
       <c r="D35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D35</f>
-        <v>60700.217828077599</v>
+        <v>64228.094068532191</v>
       </c>
     </row>
   </sheetData>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A14F47C-278C-4973-AEF6-1596F88025DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6930EF-8D98-4938-A33C-7AE7CE370EFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -263,13 +263,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B9">
-            <v>148111.95033115722</v>
+            <v>156446.61372286209</v>
           </cell>
           <cell r="C9">
             <v>13781.46783678359</v>
           </cell>
           <cell r="D9">
-            <v>10.747182526946604</v>
+            <v>11.351955798590366</v>
           </cell>
         </row>
         <row r="10">
@@ -277,13 +277,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B10">
-            <v>319614.24010068353</v>
+            <v>307085.5970910507</v>
           </cell>
           <cell r="C10">
             <v>3833.3433721023121</v>
           </cell>
           <cell r="D10">
-            <v>83.377409502816903</v>
+            <v>80.109076407271189</v>
           </cell>
         </row>
         <row r="12">
@@ -401,13 +401,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B24">
-            <v>148111.95033115722</v>
+            <v>156446.61372286209</v>
           </cell>
           <cell r="C24">
-            <v>467726.19043184072</v>
+            <v>463532.2108139128</v>
           </cell>
           <cell r="D24">
-            <v>0.3166637946752755</v>
+            <v>0.337509692040945</v>
           </cell>
         </row>
         <row r="25">
@@ -415,10 +415,10 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B25">
-            <v>319614.24010068353</v>
+            <v>307085.5970910507</v>
           </cell>
           <cell r="D25">
-            <v>0.68333620532472461</v>
+            <v>0.66249030795905506</v>
           </cell>
         </row>
         <row r="27">
@@ -445,13 +445,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B29">
-            <v>10.747182526946604</v>
+            <v>11.351955798590366</v>
           </cell>
           <cell r="C29">
             <v>10</v>
           </cell>
           <cell r="D29">
-            <v>0.74718252694660414</v>
+            <v>1.3519557985903656</v>
           </cell>
         </row>
         <row r="30">
@@ -459,13 +459,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B30">
-            <v>83.377409502816903</v>
+            <v>80.109076407271189</v>
           </cell>
           <cell r="C30">
             <v>15</v>
           </cell>
           <cell r="D30">
-            <v>68.377409502816903</v>
+            <v>65.109076407271189</v>
           </cell>
         </row>
         <row r="32">
@@ -492,13 +492,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B34">
-            <v>148111.95033115722</v>
+            <v>156446.61372286209</v>
           </cell>
           <cell r="C34">
             <v>120104.39150000001</v>
           </cell>
           <cell r="D34">
-            <v>127098.87498460655</v>
+            <v>148842.44205079641</v>
           </cell>
         </row>
         <row r="35">
@@ -506,13 +506,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B35">
-            <v>319614.24010068353</v>
+            <v>307085.5970910507</v>
           </cell>
           <cell r="C35">
             <v>104004.71860786516</v>
           </cell>
           <cell r="D35">
-            <v>64228.094068532191</v>
+            <v>75834.219078165057</v>
           </cell>
         </row>
       </sheetData>
@@ -952,7 +952,7 @@
       </c>
       <c r="B9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B9</f>
-        <v>148111.95033115722</v>
+        <v>156446.61372286209</v>
       </c>
       <c r="C9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C9</f>
@@ -960,7 +960,7 @@
       </c>
       <c r="D9" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D9</f>
-        <v>10.747182526946604</v>
+        <v>11.351955798590366</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -970,7 +970,7 @@
       </c>
       <c r="B10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B10</f>
-        <v>319614.24010068353</v>
+        <v>307085.5970910507</v>
       </c>
       <c r="C10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C10</f>
@@ -978,7 +978,7 @@
       </c>
       <c r="D10" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D10</f>
-        <v>83.377409502816903</v>
+        <v>80.109076407271189</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1138,15 +1138,15 @@
       </c>
       <c r="B24" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B24</f>
-        <v>148111.95033115722</v>
+        <v>156446.61372286209</v>
       </c>
       <c r="C24" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C24</f>
-        <v>467726.19043184072</v>
+        <v>463532.2108139128</v>
       </c>
       <c r="D24" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D24</f>
-        <v>0.3166637946752755</v>
+        <v>0.337509692040945</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B25" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B25</f>
-        <v>319614.24010068353</v>
+        <v>307085.5970910507</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D25</f>
-        <v>0.68333620532472461</v>
+        <v>0.66249030795905506</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B29" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B29</f>
-        <v>10.747182526946604</v>
+        <v>11.351955798590366</v>
       </c>
       <c r="C29" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C29</f>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="D29" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D29</f>
-        <v>0.74718252694660414</v>
+        <v>1.3519557985903656</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B30" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B30</f>
-        <v>83.377409502816903</v>
+        <v>80.109076407271189</v>
       </c>
       <c r="C30" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C30</f>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="D30" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D30</f>
-        <v>68.377409502816903</v>
+        <v>65.109076407271189</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B34</f>
-        <v>148111.95033115722</v>
+        <v>156446.61372286209</v>
       </c>
       <c r="C34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C34</f>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="D34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D34</f>
-        <v>127098.87498460655</v>
+        <v>148842.44205079641</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="B35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B35</f>
-        <v>319614.24010068353</v>
+        <v>307085.5970910507</v>
       </c>
       <c r="C35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C35</f>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="D35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D35</f>
-        <v>64228.094068532191</v>
+        <v>75834.219078165057</v>
       </c>
     </row>
   </sheetData>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6930EF-8D98-4938-A33C-7AE7CE370EFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88513A0F-F129-48FD-96FE-18105640F693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -263,13 +263,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B9">
-            <v>156446.61372286209</v>
+            <v>131638.64120611723</v>
           </cell>
           <cell r="C9">
             <v>13781.46783678359</v>
           </cell>
           <cell r="D9">
-            <v>11.351955798590366</v>
+            <v>9.5518592623904368</v>
           </cell>
         </row>
         <row r="10">
@@ -277,13 +277,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B10">
-            <v>307085.5970910507</v>
+            <v>352222.17704300617</v>
           </cell>
           <cell r="C10">
             <v>3833.3433721023121</v>
           </cell>
           <cell r="D10">
-            <v>80.109076407271189</v>
+            <v>91.883805558967637</v>
           </cell>
         </row>
         <row r="12">
@@ -401,13 +401,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B24">
-            <v>156446.61372286209</v>
+            <v>131638.64120611723</v>
           </cell>
           <cell r="C24">
-            <v>463532.2108139128</v>
+            <v>483860.8182491234</v>
           </cell>
           <cell r="D24">
-            <v>0.337509692040945</v>
+            <v>0.27205889842963271</v>
           </cell>
         </row>
         <row r="25">
@@ -415,10 +415,10 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B25">
-            <v>307085.5970910507</v>
+            <v>352222.17704300617</v>
           </cell>
           <cell r="D25">
-            <v>0.66249030795905506</v>
+            <v>0.72794110157036729</v>
           </cell>
         </row>
         <row r="27">
@@ -445,13 +445,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B29">
-            <v>11.351955798590366</v>
+            <v>9.5518592623904368</v>
           </cell>
           <cell r="C29">
             <v>10</v>
           </cell>
           <cell r="D29">
-            <v>1.3519557985903656</v>
+            <v>-0.44814073760956319</v>
           </cell>
         </row>
         <row r="30">
@@ -459,13 +459,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B30">
-            <v>80.109076407271189</v>
+            <v>91.883805558967637</v>
           </cell>
           <cell r="C30">
             <v>15</v>
           </cell>
           <cell r="D30">
-            <v>65.109076407271189</v>
+            <v>76.883805558967637</v>
           </cell>
         </row>
         <row r="32">
@@ -492,13 +492,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B34">
-            <v>156446.61372286209</v>
+            <v>131638.64120611723</v>
           </cell>
           <cell r="C34">
             <v>120104.39150000001</v>
           </cell>
           <cell r="D34">
-            <v>148842.44205079641</v>
+            <v>165299.89988333068</v>
           </cell>
         </row>
         <row r="35">
@@ -506,13 +506,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B35">
-            <v>307085.5970910507</v>
+            <v>352222.17704300617</v>
           </cell>
           <cell r="C35">
             <v>104004.71860786516</v>
           </cell>
           <cell r="D35">
-            <v>75834.219078165057</v>
+            <v>85122.363336209557</v>
           </cell>
         </row>
       </sheetData>
@@ -952,7 +952,7 @@
       </c>
       <c r="B9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B9</f>
-        <v>156446.61372286209</v>
+        <v>131638.64120611723</v>
       </c>
       <c r="C9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C9</f>
@@ -960,7 +960,7 @@
       </c>
       <c r="D9" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D9</f>
-        <v>11.351955798590366</v>
+        <v>9.5518592623904368</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -970,7 +970,7 @@
       </c>
       <c r="B10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B10</f>
-        <v>307085.5970910507</v>
+        <v>352222.17704300617</v>
       </c>
       <c r="C10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C10</f>
@@ -978,7 +978,7 @@
       </c>
       <c r="D10" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D10</f>
-        <v>80.109076407271189</v>
+        <v>91.883805558967637</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1138,15 +1138,15 @@
       </c>
       <c r="B24" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B24</f>
-        <v>156446.61372286209</v>
+        <v>131638.64120611723</v>
       </c>
       <c r="C24" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C24</f>
-        <v>463532.2108139128</v>
+        <v>483860.8182491234</v>
       </c>
       <c r="D24" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D24</f>
-        <v>0.337509692040945</v>
+        <v>0.27205889842963271</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B25" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B25</f>
-        <v>307085.5970910507</v>
+        <v>352222.17704300617</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D25</f>
-        <v>0.66249030795905506</v>
+        <v>0.72794110157036729</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B29" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B29</f>
-        <v>11.351955798590366</v>
+        <v>9.5518592623904368</v>
       </c>
       <c r="C29" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C29</f>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="D29" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D29</f>
-        <v>1.3519557985903656</v>
+        <v>-0.44814073760956319</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B30" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B30</f>
-        <v>80.109076407271189</v>
+        <v>91.883805558967637</v>
       </c>
       <c r="C30" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C30</f>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="D30" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D30</f>
-        <v>65.109076407271189</v>
+        <v>76.883805558967637</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B34</f>
-        <v>156446.61372286209</v>
+        <v>131638.64120611723</v>
       </c>
       <c r="C34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C34</f>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="D34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D34</f>
-        <v>148842.44205079641</v>
+        <v>165299.89988333068</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="B35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B35</f>
-        <v>307085.5970910507</v>
+        <v>352222.17704300617</v>
       </c>
       <c r="C35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C35</f>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="D35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D35</f>
-        <v>75834.219078165057</v>
+        <v>85122.363336209557</v>
       </c>
     </row>
   </sheetData>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88513A0F-F129-48FD-96FE-18105640F693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F4B8C81-ABE3-4BC6-8010-CBB7B8E59D43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -263,13 +263,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B9">
-            <v>131638.64120611723</v>
+            <v>81339.133312516846</v>
           </cell>
           <cell r="C9">
-            <v>13781.46783678359</v>
+            <v>15307</v>
           </cell>
           <cell r="D9">
-            <v>9.5518592623904368</v>
+            <v>5.3138520489002969</v>
           </cell>
         </row>
         <row r="10">
@@ -277,13 +277,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B10">
-            <v>352222.17704300617</v>
+            <v>340324.72064911062</v>
           </cell>
           <cell r="C10">
-            <v>3833.3433721023121</v>
+            <v>7348</v>
           </cell>
           <cell r="D10">
-            <v>91.883805558967637</v>
+            <v>46.315285880390668</v>
           </cell>
         </row>
         <row r="12">
@@ -310,13 +310,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B14">
-            <v>120104.39150000001</v>
+            <v>121408.35950000001</v>
           </cell>
           <cell r="C14">
             <v>344799.25199999998</v>
           </cell>
           <cell r="D14">
-            <v>0.34833135745897736</v>
+            <v>0.35211317540793274</v>
           </cell>
         </row>
         <row r="15">
@@ -401,13 +401,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B24">
-            <v>131638.64120611723</v>
+            <v>81339.133312516846</v>
           </cell>
           <cell r="C24">
-            <v>483860.8182491234</v>
+            <v>421663.85396162746</v>
           </cell>
           <cell r="D24">
-            <v>0.27205889842963271</v>
+            <v>0.19290041711737266</v>
           </cell>
         </row>
         <row r="25">
@@ -415,10 +415,10 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B25">
-            <v>352222.17704300617</v>
+            <v>340324.72064911062</v>
           </cell>
           <cell r="D25">
-            <v>0.72794110157036729</v>
+            <v>0.8070995828826274</v>
           </cell>
         </row>
         <row r="27">
@@ -445,13 +445,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B29">
-            <v>9.5518592623904368</v>
+            <v>5.3138520489002969</v>
           </cell>
           <cell r="C29">
             <v>10</v>
           </cell>
           <cell r="D29">
-            <v>-0.44814073760956319</v>
+            <v>-4.6861479510997031</v>
           </cell>
         </row>
         <row r="30">
@@ -459,13 +459,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B30">
-            <v>91.883805558967637</v>
+            <v>46.315285880390668</v>
           </cell>
           <cell r="C30">
             <v>15</v>
           </cell>
           <cell r="D30">
-            <v>76.883805558967637</v>
+            <v>31.315285880390668</v>
           </cell>
         </row>
         <row r="32">
@@ -492,13 +492,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B34">
-            <v>131638.64120611723</v>
+            <v>81339.133312516846</v>
           </cell>
           <cell r="C34">
-            <v>120104.39150000001</v>
+            <v>121408.35950000001</v>
           </cell>
           <cell r="D34">
-            <v>165299.89988333068</v>
+            <v>188430.57493772055</v>
           </cell>
         </row>
         <row r="35">
@@ -506,13 +506,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B35">
-            <v>352222.17704300617</v>
+            <v>340324.72064911062</v>
           </cell>
           <cell r="C35">
             <v>104004.71860786516</v>
           </cell>
           <cell r="D35">
-            <v>85122.363336209557</v>
+            <v>94114.379730105109</v>
           </cell>
         </row>
       </sheetData>
@@ -952,15 +952,15 @@
       </c>
       <c r="B9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B9</f>
-        <v>131638.64120611723</v>
+        <v>81339.133312516846</v>
       </c>
       <c r="C9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C9</f>
-        <v>13781.46783678359</v>
+        <v>15307</v>
       </c>
       <c r="D9" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D9</f>
-        <v>9.5518592623904368</v>
+        <v>5.3138520489002969</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -970,15 +970,15 @@
       </c>
       <c r="B10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B10</f>
-        <v>352222.17704300617</v>
+        <v>340324.72064911062</v>
       </c>
       <c r="C10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C10</f>
-        <v>3833.3433721023121</v>
+        <v>7348</v>
       </c>
       <c r="D10" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D10</f>
-        <v>91.883805558967637</v>
+        <v>46.315285880390668</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B14</f>
-        <v>120104.39150000001</v>
+        <v>121408.35950000001</v>
       </c>
       <c r="C14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C14</f>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="D14" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D14</f>
-        <v>0.34833135745897736</v>
+        <v>0.35211317540793274</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1138,15 +1138,15 @@
       </c>
       <c r="B24" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B24</f>
-        <v>131638.64120611723</v>
+        <v>81339.133312516846</v>
       </c>
       <c r="C24" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C24</f>
-        <v>483860.8182491234</v>
+        <v>421663.85396162746</v>
       </c>
       <c r="D24" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D24</f>
-        <v>0.27205889842963271</v>
+        <v>0.19290041711737266</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B25" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B25</f>
-        <v>352222.17704300617</v>
+        <v>340324.72064911062</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D25</f>
-        <v>0.72794110157036729</v>
+        <v>0.8070995828826274</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B29" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B29</f>
-        <v>9.5518592623904368</v>
+        <v>5.3138520489002969</v>
       </c>
       <c r="C29" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C29</f>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="D29" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D29</f>
-        <v>-0.44814073760956319</v>
+        <v>-4.6861479510997031</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B30" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B30</f>
-        <v>91.883805558967637</v>
+        <v>46.315285880390668</v>
       </c>
       <c r="C30" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C30</f>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="D30" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D30</f>
-        <v>76.883805558967637</v>
+        <v>31.315285880390668</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1261,15 +1261,15 @@
       </c>
       <c r="B34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B34</f>
-        <v>131638.64120611723</v>
+        <v>81339.133312516846</v>
       </c>
       <c r="C34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C34</f>
-        <v>120104.39150000001</v>
+        <v>121408.35950000001</v>
       </c>
       <c r="D34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D34</f>
-        <v>165299.89988333068</v>
+        <v>188430.57493772055</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="B35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B35</f>
-        <v>352222.17704300617</v>
+        <v>340324.72064911062</v>
       </c>
       <c r="C35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C35</f>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="D35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D35</f>
-        <v>85122.363336209557</v>
+        <v>94114.379730105109</v>
       </c>
     </row>
   </sheetData>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F4B8C81-ABE3-4BC6-8010-CBB7B8E59D43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D12AFE97-8F10-4BE1-969F-B083FACF7652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -263,13 +263,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B9">
-            <v>81339.133312516846</v>
+            <v>74682.126015793518</v>
           </cell>
           <cell r="C9">
             <v>15307</v>
           </cell>
           <cell r="D9">
-            <v>5.3138520489002969</v>
+            <v>4.8789525064214754</v>
           </cell>
         </row>
         <row r="10">
@@ -277,13 +277,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B10">
-            <v>340324.72064911062</v>
+            <v>340342.07687351556</v>
           </cell>
           <cell r="C10">
             <v>7348</v>
           </cell>
           <cell r="D10">
-            <v>46.315285880390668</v>
+            <v>46.317647914196456</v>
           </cell>
         </row>
         <row r="12">
@@ -310,13 +310,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B14">
-            <v>121408.35950000001</v>
+            <v>121443.3245</v>
           </cell>
           <cell r="C14">
             <v>344799.25199999998</v>
           </cell>
           <cell r="D14">
-            <v>0.35211317540793274</v>
+            <v>0.35221458224045105</v>
           </cell>
         </row>
         <row r="15">
@@ -324,13 +324,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B15">
-            <v>104004.71860786516</v>
+            <v>110743.91860786518</v>
           </cell>
           <cell r="C15">
             <v>108924.24443806437</v>
           </cell>
           <cell r="D15">
-            <v>0.95483534583527441</v>
+            <v>1.0167058691036917</v>
           </cell>
         </row>
         <row r="17">
@@ -401,13 +401,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B24">
-            <v>81339.133312516846</v>
+            <v>74682.126015793518</v>
           </cell>
           <cell r="C24">
-            <v>421663.85396162746</v>
+            <v>415024.20288930909</v>
           </cell>
           <cell r="D24">
-            <v>0.19290041711737266</v>
+            <v>0.1799464356436869</v>
           </cell>
         </row>
         <row r="25">
@@ -415,10 +415,10 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B25">
-            <v>340324.72064911062</v>
+            <v>340342.07687351556</v>
           </cell>
           <cell r="D25">
-            <v>0.8070995828826274</v>
+            <v>0.82005356435631305</v>
           </cell>
         </row>
         <row r="27">
@@ -445,13 +445,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B29">
-            <v>5.3138520489002969</v>
+            <v>4.8789525064214754</v>
           </cell>
           <cell r="C29">
             <v>10</v>
           </cell>
           <cell r="D29">
-            <v>-4.6861479510997031</v>
+            <v>-5.1210474935785246</v>
           </cell>
         </row>
         <row r="30">
@@ -459,13 +459,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B30">
-            <v>46.315285880390668</v>
+            <v>46.317647914196456</v>
           </cell>
           <cell r="C30">
             <v>15</v>
           </cell>
           <cell r="D30">
-            <v>31.315285880390668</v>
+            <v>31.317647914196456</v>
           </cell>
         </row>
         <row r="32">
@@ -492,13 +492,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B34">
-            <v>81339.133312516846</v>
+            <v>74682.126015793518</v>
           </cell>
           <cell r="C34">
-            <v>121408.35950000001</v>
+            <v>121443.3245</v>
           </cell>
           <cell r="D34">
-            <v>188430.57493772055</v>
+            <v>197562.54805286491</v>
           </cell>
         </row>
         <row r="35">
@@ -506,13 +506,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B35">
-            <v>340324.72064911062</v>
+            <v>340342.07687351556</v>
           </cell>
           <cell r="C35">
-            <v>104004.71860786516</v>
+            <v>110743.91860786518</v>
           </cell>
           <cell r="D35">
-            <v>94114.379730105109</v>
+            <v>97389.675902141506</v>
           </cell>
         </row>
       </sheetData>
@@ -952,7 +952,7 @@
       </c>
       <c r="B9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B9</f>
-        <v>81339.133312516846</v>
+        <v>74682.126015793518</v>
       </c>
       <c r="C9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C9</f>
@@ -960,7 +960,7 @@
       </c>
       <c r="D9" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D9</f>
-        <v>5.3138520489002969</v>
+        <v>4.8789525064214754</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -970,7 +970,7 @@
       </c>
       <c r="B10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B10</f>
-        <v>340324.72064911062</v>
+        <v>340342.07687351556</v>
       </c>
       <c r="C10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C10</f>
@@ -978,7 +978,7 @@
       </c>
       <c r="D10" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D10</f>
-        <v>46.315285880390668</v>
+        <v>46.317647914196456</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B14</f>
-        <v>121408.35950000001</v>
+        <v>121443.3245</v>
       </c>
       <c r="C14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C14</f>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="D14" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D14</f>
-        <v>0.35211317540793274</v>
+        <v>0.35221458224045105</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B15" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B15</f>
-        <v>104004.71860786516</v>
+        <v>110743.91860786518</v>
       </c>
       <c r="C15" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C15</f>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="D15" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D15</f>
-        <v>0.95483534583527441</v>
+        <v>1.0167058691036917</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1138,15 +1138,15 @@
       </c>
       <c r="B24" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B24</f>
-        <v>81339.133312516846</v>
+        <v>74682.126015793518</v>
       </c>
       <c r="C24" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C24</f>
-        <v>421663.85396162746</v>
+        <v>415024.20288930909</v>
       </c>
       <c r="D24" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D24</f>
-        <v>0.19290041711737266</v>
+        <v>0.1799464356436869</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B25" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B25</f>
-        <v>340324.72064911062</v>
+        <v>340342.07687351556</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D25</f>
-        <v>0.8070995828826274</v>
+        <v>0.82005356435631305</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B29" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B29</f>
-        <v>5.3138520489002969</v>
+        <v>4.8789525064214754</v>
       </c>
       <c r="C29" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C29</f>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="D29" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D29</f>
-        <v>-4.6861479510997031</v>
+        <v>-5.1210474935785246</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B30" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B30</f>
-        <v>46.315285880390668</v>
+        <v>46.317647914196456</v>
       </c>
       <c r="C30" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C30</f>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="D30" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D30</f>
-        <v>31.315285880390668</v>
+        <v>31.317647914196456</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1261,15 +1261,15 @@
       </c>
       <c r="B34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B34</f>
-        <v>81339.133312516846</v>
+        <v>74682.126015793518</v>
       </c>
       <c r="C34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C34</f>
-        <v>121408.35950000001</v>
+        <v>121443.3245</v>
       </c>
       <c r="D34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D34</f>
-        <v>188430.57493772055</v>
+        <v>197562.54805286491</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1279,15 +1279,15 @@
       </c>
       <c r="B35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B35</f>
-        <v>340324.72064911062</v>
+        <v>340342.07687351556</v>
       </c>
       <c r="C35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C35</f>
-        <v>104004.71860786516</v>
+        <v>110743.91860786518</v>
       </c>
       <c r="D35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D35</f>
-        <v>94114.379730105109</v>
+        <v>97389.675902141506</v>
       </c>
     </row>
   </sheetData>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D12AFE97-8F10-4BE1-969F-B083FACF7652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2731BFF2-856C-46FE-AA58-5181DD58F405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -263,13 +263,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B9">
-            <v>74682.126015793518</v>
+            <v>116128.90358097706</v>
           </cell>
           <cell r="C9">
             <v>15307</v>
           </cell>
           <cell r="D9">
-            <v>4.8789525064214754</v>
+            <v>7.5866533991622829</v>
           </cell>
         </row>
         <row r="10">
@@ -277,13 +277,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B10">
-            <v>340342.07687351556</v>
+            <v>319879.700822627</v>
           </cell>
           <cell r="C10">
             <v>7348</v>
           </cell>
           <cell r="D10">
-            <v>46.317647914196456</v>
+            <v>43.532893416252996</v>
           </cell>
         </row>
         <row r="12">
@@ -310,13 +310,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B14">
-            <v>121443.3245</v>
+            <v>191058.36749999999</v>
           </cell>
           <cell r="C14">
             <v>344799.25199999998</v>
           </cell>
           <cell r="D14">
-            <v>0.35221458224045105</v>
+            <v>0.55411479691957111</v>
           </cell>
         </row>
         <row r="15">
@@ -401,13 +401,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B24">
-            <v>74682.126015793518</v>
+            <v>116128.90358097706</v>
           </cell>
           <cell r="C24">
-            <v>415024.20288930909</v>
+            <v>436008.60440360405</v>
           </cell>
           <cell r="D24">
-            <v>0.1799464356436869</v>
+            <v>0.26634543999383775</v>
           </cell>
         </row>
         <row r="25">
@@ -415,10 +415,10 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B25">
-            <v>340342.07687351556</v>
+            <v>319879.700822627</v>
           </cell>
           <cell r="D25">
-            <v>0.82005356435631305</v>
+            <v>0.73365456000616225</v>
           </cell>
         </row>
         <row r="27">
@@ -445,13 +445,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B29">
-            <v>4.8789525064214754</v>
+            <v>7.5866533991622829</v>
           </cell>
           <cell r="C29">
             <v>10</v>
           </cell>
           <cell r="D29">
-            <v>-5.1210474935785246</v>
+            <v>-2.4133466008377171</v>
           </cell>
         </row>
         <row r="30">
@@ -459,13 +459,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B30">
-            <v>46.317647914196456</v>
+            <v>43.532893416252996</v>
           </cell>
           <cell r="C30">
             <v>15</v>
           </cell>
           <cell r="D30">
-            <v>31.317647914196456</v>
+            <v>28.532893416252996</v>
           </cell>
         </row>
         <row r="32">
@@ -492,13 +492,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B34">
-            <v>74682.126015793518</v>
+            <v>116128.90358097706</v>
           </cell>
           <cell r="C34">
-            <v>121443.3245</v>
+            <v>191058.36749999999</v>
           </cell>
           <cell r="D34">
-            <v>197562.54805286491</v>
+            <v>219454.98399189193</v>
           </cell>
         </row>
         <row r="35">
@@ -506,13 +506,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B35">
-            <v>340342.07687351556</v>
+            <v>319879.700822627</v>
           </cell>
           <cell r="C35">
             <v>110743.91860786518</v>
           </cell>
           <cell r="D35">
-            <v>97389.675902141506</v>
+            <v>107665.97519650226</v>
           </cell>
         </row>
       </sheetData>
@@ -952,7 +952,7 @@
       </c>
       <c r="B9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B9</f>
-        <v>74682.126015793518</v>
+        <v>116128.90358097706</v>
       </c>
       <c r="C9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C9</f>
@@ -960,7 +960,7 @@
       </c>
       <c r="D9" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D9</f>
-        <v>4.8789525064214754</v>
+        <v>7.5866533991622829</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -970,7 +970,7 @@
       </c>
       <c r="B10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B10</f>
-        <v>340342.07687351556</v>
+        <v>319879.700822627</v>
       </c>
       <c r="C10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C10</f>
@@ -978,7 +978,7 @@
       </c>
       <c r="D10" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D10</f>
-        <v>46.317647914196456</v>
+        <v>43.532893416252996</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B14</f>
-        <v>121443.3245</v>
+        <v>191058.36749999999</v>
       </c>
       <c r="C14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C14</f>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="D14" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D14</f>
-        <v>0.35221458224045105</v>
+        <v>0.55411479691957111</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1138,15 +1138,15 @@
       </c>
       <c r="B24" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B24</f>
-        <v>74682.126015793518</v>
+        <v>116128.90358097706</v>
       </c>
       <c r="C24" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C24</f>
-        <v>415024.20288930909</v>
+        <v>436008.60440360405</v>
       </c>
       <c r="D24" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D24</f>
-        <v>0.1799464356436869</v>
+        <v>0.26634543999383775</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B25" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B25</f>
-        <v>340342.07687351556</v>
+        <v>319879.700822627</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D25</f>
-        <v>0.82005356435631305</v>
+        <v>0.73365456000616225</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B29" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B29</f>
-        <v>4.8789525064214754</v>
+        <v>7.5866533991622829</v>
       </c>
       <c r="C29" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C29</f>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="D29" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D29</f>
-        <v>-5.1210474935785246</v>
+        <v>-2.4133466008377171</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B30" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B30</f>
-        <v>46.317647914196456</v>
+        <v>43.532893416252996</v>
       </c>
       <c r="C30" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C30</f>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="D30" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D30</f>
-        <v>31.317647914196456</v>
+        <v>28.532893416252996</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1261,15 +1261,15 @@
       </c>
       <c r="B34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B34</f>
-        <v>74682.126015793518</v>
+        <v>116128.90358097706</v>
       </c>
       <c r="C34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C34</f>
-        <v>121443.3245</v>
+        <v>191058.36749999999</v>
       </c>
       <c r="D34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D34</f>
-        <v>197562.54805286491</v>
+        <v>219454.98399189193</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="B35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B35</f>
-        <v>340342.07687351556</v>
+        <v>319879.700822627</v>
       </c>
       <c r="C35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C35</f>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="D35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D35</f>
-        <v>97389.675902141506</v>
+        <v>107665.97519650226</v>
       </c>
     </row>
   </sheetData>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2731BFF2-856C-46FE-AA58-5181DD58F405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA956A1-09AA-4AFC-A53D-263E8FA26297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -263,13 +263,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B9">
-            <v>116128.90358097706</v>
+            <v>97360.140274092671</v>
           </cell>
           <cell r="C9">
             <v>15307</v>
           </cell>
           <cell r="D9">
-            <v>7.5866533991622829</v>
+            <v>6.3604978293651708</v>
           </cell>
         </row>
         <row r="10">
@@ -277,13 +277,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B10">
-            <v>319879.700822627</v>
+            <v>314026.63187927671</v>
           </cell>
           <cell r="C10">
             <v>7348</v>
           </cell>
           <cell r="D10">
-            <v>43.532893416252996</v>
+            <v>42.736340756570051</v>
           </cell>
         </row>
         <row r="12">
@@ -401,13 +401,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B24">
-            <v>116128.90358097706</v>
+            <v>97360.140274092671</v>
           </cell>
           <cell r="C24">
-            <v>436008.60440360405</v>
+            <v>411386.77215336938</v>
           </cell>
           <cell r="D24">
-            <v>0.26634543999383775</v>
+            <v>0.23666327374715823</v>
           </cell>
         </row>
         <row r="25">
@@ -415,10 +415,10 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B25">
-            <v>319879.700822627</v>
+            <v>314026.63187927671</v>
           </cell>
           <cell r="D25">
-            <v>0.73365456000616225</v>
+            <v>0.76333672625284177</v>
           </cell>
         </row>
         <row r="27">
@@ -445,13 +445,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B29">
-            <v>7.5866533991622829</v>
+            <v>6.3604978293651708</v>
           </cell>
           <cell r="C29">
             <v>10</v>
           </cell>
           <cell r="D29">
-            <v>-2.4133466008377171</v>
+            <v>-3.6395021706348292</v>
           </cell>
         </row>
         <row r="30">
@@ -459,13 +459,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B30">
-            <v>43.532893416252996</v>
+            <v>42.736340756570051</v>
           </cell>
           <cell r="C30">
             <v>15</v>
           </cell>
           <cell r="D30">
-            <v>28.532893416252996</v>
+            <v>27.736340756570051</v>
           </cell>
         </row>
         <row r="32">
@@ -492,13 +492,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B34">
-            <v>116128.90358097706</v>
+            <v>97360.140274092671</v>
           </cell>
           <cell r="C34">
             <v>191058.36749999999</v>
           </cell>
           <cell r="D34">
-            <v>219454.98399189193</v>
+            <v>239495.61475535523</v>
           </cell>
         </row>
         <row r="35">
@@ -506,13 +506,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B35">
-            <v>319879.700822627</v>
+            <v>314026.63187927671</v>
           </cell>
           <cell r="C35">
             <v>110743.91860786518</v>
           </cell>
           <cell r="D35">
-            <v>107665.97519650226</v>
+            <v>117052.4802572484</v>
           </cell>
         </row>
       </sheetData>
@@ -952,7 +952,7 @@
       </c>
       <c r="B9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B9</f>
-        <v>116128.90358097706</v>
+        <v>97360.140274092671</v>
       </c>
       <c r="C9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C9</f>
@@ -960,7 +960,7 @@
       </c>
       <c r="D9" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D9</f>
-        <v>7.5866533991622829</v>
+        <v>6.3604978293651708</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -970,7 +970,7 @@
       </c>
       <c r="B10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B10</f>
-        <v>319879.700822627</v>
+        <v>314026.63187927671</v>
       </c>
       <c r="C10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C10</f>
@@ -978,7 +978,7 @@
       </c>
       <c r="D10" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D10</f>
-        <v>43.532893416252996</v>
+        <v>42.736340756570051</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1138,15 +1138,15 @@
       </c>
       <c r="B24" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B24</f>
-        <v>116128.90358097706</v>
+        <v>97360.140274092671</v>
       </c>
       <c r="C24" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C24</f>
-        <v>436008.60440360405</v>
+        <v>411386.77215336938</v>
       </c>
       <c r="D24" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D24</f>
-        <v>0.26634543999383775</v>
+        <v>0.23666327374715823</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B25" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B25</f>
-        <v>319879.700822627</v>
+        <v>314026.63187927671</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D25</f>
-        <v>0.73365456000616225</v>
+        <v>0.76333672625284177</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B29" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B29</f>
-        <v>7.5866533991622829</v>
+        <v>6.3604978293651708</v>
       </c>
       <c r="C29" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C29</f>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="D29" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D29</f>
-        <v>-2.4133466008377171</v>
+        <v>-3.6395021706348292</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B30" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B30</f>
-        <v>43.532893416252996</v>
+        <v>42.736340756570051</v>
       </c>
       <c r="C30" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C30</f>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="D30" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D30</f>
-        <v>28.532893416252996</v>
+        <v>27.736340756570051</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B34</f>
-        <v>116128.90358097706</v>
+        <v>97360.140274092671</v>
       </c>
       <c r="C34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C34</f>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="D34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D34</f>
-        <v>219454.98399189193</v>
+        <v>239495.61475535523</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="B35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B35</f>
-        <v>319879.700822627</v>
+        <v>314026.63187927671</v>
       </c>
       <c r="C35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C35</f>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="D35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D35</f>
-        <v>107665.97519650226</v>
+        <v>117052.4802572484</v>
       </c>
     </row>
   </sheetData>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA956A1-09AA-4AFC-A53D-263E8FA26297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD14CE5A-6650-4C1C-97A2-69B5E0C77395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -263,13 +263,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B9">
-            <v>97360.140274092671</v>
+            <v>86478.708558612983</v>
           </cell>
           <cell r="C9">
             <v>15307</v>
           </cell>
           <cell r="D9">
-            <v>6.3604978293651708</v>
+            <v>5.6496183810422016</v>
           </cell>
         </row>
         <row r="10">
@@ -277,13 +277,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B10">
-            <v>314026.63187927671</v>
+            <v>304966.162957369</v>
           </cell>
           <cell r="C10">
             <v>7348</v>
           </cell>
           <cell r="D10">
-            <v>42.736340756570051</v>
+            <v>41.503288371988162</v>
           </cell>
         </row>
         <row r="12">
@@ -401,13 +401,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B24">
-            <v>97360.140274092671</v>
+            <v>86478.708558612983</v>
           </cell>
           <cell r="C24">
-            <v>411386.77215336938</v>
+            <v>391444.87151598197</v>
           </cell>
           <cell r="D24">
-            <v>0.23666327374715823</v>
+            <v>0.22092180751710835</v>
           </cell>
         </row>
         <row r="25">
@@ -415,10 +415,10 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B25">
-            <v>314026.63187927671</v>
+            <v>304966.162957369</v>
           </cell>
           <cell r="D25">
-            <v>0.76333672625284177</v>
+            <v>0.77907819248289167</v>
           </cell>
         </row>
         <row r="27">
@@ -445,13 +445,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B29">
-            <v>6.3604978293651708</v>
+            <v>5.6496183810422016</v>
           </cell>
           <cell r="C29">
             <v>10</v>
           </cell>
           <cell r="D29">
-            <v>-3.6395021706348292</v>
+            <v>-4.3503816189577984</v>
           </cell>
         </row>
         <row r="30">
@@ -459,13 +459,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B30">
-            <v>42.736340756570051</v>
+            <v>41.503288371988162</v>
           </cell>
           <cell r="C30">
             <v>15</v>
           </cell>
           <cell r="D30">
-            <v>27.736340756570051</v>
+            <v>26.503288371988162</v>
           </cell>
         </row>
         <row r="32">
@@ -492,13 +492,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B34">
-            <v>97360.140274092671</v>
+            <v>86478.708558612983</v>
           </cell>
           <cell r="C34">
             <v>191058.36749999999</v>
           </cell>
           <cell r="D34">
-            <v>239495.61475535523</v>
+            <v>254046.48736557167</v>
           </cell>
         </row>
         <row r="35">
@@ -506,13 +506,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B35">
-            <v>314026.63187927671</v>
+            <v>304966.162957369</v>
           </cell>
           <cell r="C35">
             <v>110743.91860786518</v>
           </cell>
           <cell r="D35">
-            <v>117052.4802572484</v>
+            <v>126113.30017915615</v>
           </cell>
         </row>
       </sheetData>
@@ -952,7 +952,7 @@
       </c>
       <c r="B9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B9</f>
-        <v>97360.140274092671</v>
+        <v>86478.708558612983</v>
       </c>
       <c r="C9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C9</f>
@@ -960,7 +960,7 @@
       </c>
       <c r="D9" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D9</f>
-        <v>6.3604978293651708</v>
+        <v>5.6496183810422016</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -970,7 +970,7 @@
       </c>
       <c r="B10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B10</f>
-        <v>314026.63187927671</v>
+        <v>304966.162957369</v>
       </c>
       <c r="C10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C10</f>
@@ -978,7 +978,7 @@
       </c>
       <c r="D10" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D10</f>
-        <v>42.736340756570051</v>
+        <v>41.503288371988162</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1138,15 +1138,15 @@
       </c>
       <c r="B24" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B24</f>
-        <v>97360.140274092671</v>
+        <v>86478.708558612983</v>
       </c>
       <c r="C24" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C24</f>
-        <v>411386.77215336938</v>
+        <v>391444.87151598197</v>
       </c>
       <c r="D24" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D24</f>
-        <v>0.23666327374715823</v>
+        <v>0.22092180751710835</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B25" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B25</f>
-        <v>314026.63187927671</v>
+        <v>304966.162957369</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D25</f>
-        <v>0.76333672625284177</v>
+        <v>0.77907819248289167</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B29" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B29</f>
-        <v>6.3604978293651708</v>
+        <v>5.6496183810422016</v>
       </c>
       <c r="C29" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C29</f>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="D29" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D29</f>
-        <v>-3.6395021706348292</v>
+        <v>-4.3503816189577984</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B30" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B30</f>
-        <v>42.736340756570051</v>
+        <v>41.503288371988162</v>
       </c>
       <c r="C30" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C30</f>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="D30" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D30</f>
-        <v>27.736340756570051</v>
+        <v>26.503288371988162</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B34</f>
-        <v>97360.140274092671</v>
+        <v>86478.708558612983</v>
       </c>
       <c r="C34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C34</f>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="D34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D34</f>
-        <v>239495.61475535523</v>
+        <v>254046.48736557167</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="B35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B35</f>
-        <v>314026.63187927671</v>
+        <v>304966.162957369</v>
       </c>
       <c r="C35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C35</f>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="D35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D35</f>
-        <v>117052.4802572484</v>
+        <v>126113.30017915615</v>
       </c>
     </row>
   </sheetData>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD14CE5A-6650-4C1C-97A2-69B5E0C77395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{391DB279-065F-436D-A2CF-21E299BB32CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -230,13 +230,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B5">
-            <v>269763</v>
+            <v>321540</v>
           </cell>
           <cell r="C5">
             <v>7348</v>
           </cell>
           <cell r="D5">
-            <v>36.712438758845941</v>
+            <v>43.758845944474686</v>
           </cell>
         </row>
         <row r="7">
@@ -263,13 +263,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B9">
-            <v>86478.708558612983</v>
+            <v>91458.228558612973</v>
           </cell>
           <cell r="C9">
             <v>15307</v>
           </cell>
           <cell r="D9">
-            <v>5.6496183810422016</v>
+            <v>5.9749283699361708</v>
           </cell>
         </row>
         <row r="10">
@@ -277,13 +277,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B10">
-            <v>304966.162957369</v>
+            <v>298788.56295736902</v>
           </cell>
           <cell r="C10">
             <v>7348</v>
           </cell>
           <cell r="D10">
-            <v>41.503288371988162</v>
+            <v>40.662569809113911</v>
           </cell>
         </row>
         <row r="12">
@@ -310,13 +310,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B14">
-            <v>191058.36749999999</v>
+            <v>198171.9675</v>
           </cell>
           <cell r="C14">
             <v>344799.25199999998</v>
           </cell>
           <cell r="D14">
-            <v>0.55411479691957111</v>
+            <v>0.57474593216344916</v>
           </cell>
         </row>
         <row r="15">
@@ -360,10 +360,10 @@
             <v>154039.39212143701</v>
           </cell>
           <cell r="C19">
-            <v>423802.39212143701</v>
+            <v>475579.39212143701</v>
           </cell>
           <cell r="D19">
-            <v>0.36346985053661124</v>
+            <v>0.32389837464215387</v>
           </cell>
         </row>
         <row r="20">
@@ -371,10 +371,10 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B20">
-            <v>269763</v>
+            <v>321540</v>
           </cell>
           <cell r="D20">
-            <v>0.63653014946338882</v>
+            <v>0.67610162535784613</v>
           </cell>
         </row>
         <row r="22">
@@ -401,13 +401,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B24">
-            <v>86478.708558612983</v>
+            <v>91458.228558612973</v>
           </cell>
           <cell r="C24">
-            <v>391444.87151598197</v>
+            <v>390246.79151598201</v>
           </cell>
           <cell r="D24">
-            <v>0.22092180751710835</v>
+            <v>0.23435997565368177</v>
           </cell>
         </row>
         <row r="25">
@@ -415,10 +415,10 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B25">
-            <v>304966.162957369</v>
+            <v>298788.56295736902</v>
           </cell>
           <cell r="D25">
-            <v>0.77907819248289167</v>
+            <v>0.76564002434631817</v>
           </cell>
         </row>
         <row r="27">
@@ -445,13 +445,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B29">
-            <v>5.6496183810422016</v>
+            <v>5.9749283699361708</v>
           </cell>
           <cell r="C29">
             <v>10</v>
           </cell>
           <cell r="D29">
-            <v>-4.3503816189577984</v>
+            <v>-4.0250716300638292</v>
           </cell>
         </row>
         <row r="30">
@@ -459,13 +459,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B30">
-            <v>41.503288371988162</v>
+            <v>40.662569809113911</v>
           </cell>
           <cell r="C30">
             <v>15</v>
           </cell>
           <cell r="D30">
-            <v>26.503288371988162</v>
+            <v>25.662569809113911</v>
           </cell>
         </row>
         <row r="32">
@@ -492,10 +492,10 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B34">
-            <v>86478.708558612983</v>
+            <v>91458.228558612973</v>
           </cell>
           <cell r="C34">
-            <v>191058.36749999999</v>
+            <v>198171.9675</v>
           </cell>
           <cell r="D34">
             <v>254046.48736557167</v>
@@ -506,7 +506,7 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B35">
-            <v>304966.162957369</v>
+            <v>298788.56295736902</v>
           </cell>
           <cell r="C35">
             <v>110743.91860786518</v>
@@ -907,7 +907,7 @@
       </c>
       <c r="B5" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B5</f>
-        <v>269763</v>
+        <v>321540</v>
       </c>
       <c r="C5" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C5</f>
@@ -915,7 +915,7 @@
       </c>
       <c r="D5" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D5</f>
-        <v>36.712438758845941</v>
+        <v>43.758845944474686</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -952,7 +952,7 @@
       </c>
       <c r="B9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B9</f>
-        <v>86478.708558612983</v>
+        <v>91458.228558612973</v>
       </c>
       <c r="C9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C9</f>
@@ -960,7 +960,7 @@
       </c>
       <c r="D9" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D9</f>
-        <v>5.6496183810422016</v>
+        <v>5.9749283699361708</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -970,7 +970,7 @@
       </c>
       <c r="B10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B10</f>
-        <v>304966.162957369</v>
+        <v>298788.56295736902</v>
       </c>
       <c r="C10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C10</f>
@@ -978,7 +978,7 @@
       </c>
       <c r="D10" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D10</f>
-        <v>41.503288371988162</v>
+        <v>40.662569809113911</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B14</f>
-        <v>191058.36749999999</v>
+        <v>198171.9675</v>
       </c>
       <c r="C14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C14</f>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="D14" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D14</f>
-        <v>0.55411479691957111</v>
+        <v>0.57474593216344916</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1082,11 +1082,11 @@
       </c>
       <c r="C19" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C19</f>
-        <v>423802.39212143701</v>
+        <v>475579.39212143701</v>
       </c>
       <c r="D19" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D19</f>
-        <v>0.36346985053661124</v>
+        <v>0.32389837464215387</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B20" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B20</f>
-        <v>269763</v>
+        <v>321540</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D20</f>
-        <v>0.63653014946338882</v>
+        <v>0.67610162535784613</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1138,15 +1138,15 @@
       </c>
       <c r="B24" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B24</f>
-        <v>86478.708558612983</v>
+        <v>91458.228558612973</v>
       </c>
       <c r="C24" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C24</f>
-        <v>391444.87151598197</v>
+        <v>390246.79151598201</v>
       </c>
       <c r="D24" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D24</f>
-        <v>0.22092180751710835</v>
+        <v>0.23435997565368177</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B25" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B25</f>
-        <v>304966.162957369</v>
+        <v>298788.56295736902</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D25</f>
-        <v>0.77907819248289167</v>
+        <v>0.76564002434631817</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B29" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B29</f>
-        <v>5.6496183810422016</v>
+        <v>5.9749283699361708</v>
       </c>
       <c r="C29" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C29</f>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="D29" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D29</f>
-        <v>-4.3503816189577984</v>
+        <v>-4.0250716300638292</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B30" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B30</f>
-        <v>41.503288371988162</v>
+        <v>40.662569809113911</v>
       </c>
       <c r="C30" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C30</f>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="D30" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D30</f>
-        <v>26.503288371988162</v>
+        <v>25.662569809113911</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1261,11 +1261,11 @@
       </c>
       <c r="B34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B34</f>
-        <v>86478.708558612983</v>
+        <v>91458.228558612973</v>
       </c>
       <c r="C34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C34</f>
-        <v>191058.36749999999</v>
+        <v>198171.9675</v>
       </c>
       <c r="D34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D34</f>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="B35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B35</f>
-        <v>304966.162957369</v>
+        <v>298788.56295736902</v>
       </c>
       <c r="C35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C35</f>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{391DB279-065F-436D-A2CF-21E299BB32CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D06803-D9C6-4E8A-BE43-682447EA1831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -230,13 +230,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B5">
-            <v>321540</v>
+            <v>314158</v>
           </cell>
           <cell r="C5">
             <v>7348</v>
           </cell>
           <cell r="D5">
-            <v>43.758845944474686</v>
+            <v>42.754218835057159</v>
           </cell>
         </row>
         <row r="7">
@@ -263,13 +263,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B9">
-            <v>91458.228558612973</v>
+            <v>71317.981957891461</v>
           </cell>
           <cell r="C9">
             <v>15307</v>
           </cell>
           <cell r="D9">
-            <v>5.9749283699361708</v>
+            <v>4.6591743619188257</v>
           </cell>
         </row>
         <row r="10">
@@ -277,13 +277,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B10">
-            <v>298788.56295736902</v>
+            <v>290666.1570771393</v>
           </cell>
           <cell r="C10">
             <v>7348</v>
           </cell>
           <cell r="D10">
-            <v>40.662569809113911</v>
+            <v>39.557179787308016</v>
           </cell>
         </row>
         <row r="12">
@@ -360,10 +360,10 @@
             <v>154039.39212143701</v>
           </cell>
           <cell r="C19">
-            <v>475579.39212143701</v>
+            <v>468197.39212143701</v>
           </cell>
           <cell r="D19">
-            <v>0.32389837464215387</v>
+            <v>0.32900523307802532</v>
           </cell>
         </row>
         <row r="20">
@@ -371,10 +371,10 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B20">
-            <v>321540</v>
+            <v>314158</v>
           </cell>
           <cell r="D20">
-            <v>0.67610162535784613</v>
+            <v>0.67099476692197468</v>
           </cell>
         </row>
         <row r="22">
@@ -401,13 +401,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B24">
-            <v>91458.228558612973</v>
+            <v>71317.981957891461</v>
           </cell>
           <cell r="C24">
-            <v>390246.79151598201</v>
+            <v>361984.13903503073</v>
           </cell>
           <cell r="D24">
-            <v>0.23435997565368177</v>
+            <v>0.19701963226347252</v>
           </cell>
         </row>
         <row r="25">
@@ -415,10 +415,10 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B25">
-            <v>298788.56295736902</v>
+            <v>290666.1570771393</v>
           </cell>
           <cell r="D25">
-            <v>0.76564002434631817</v>
+            <v>0.80298036773652759</v>
           </cell>
         </row>
         <row r="27">
@@ -445,13 +445,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B29">
-            <v>5.9749283699361708</v>
+            <v>4.6591743619188257</v>
           </cell>
           <cell r="C29">
             <v>10</v>
           </cell>
           <cell r="D29">
-            <v>-4.0250716300638292</v>
+            <v>-5.3408256380811743</v>
           </cell>
         </row>
         <row r="30">
@@ -459,13 +459,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B30">
-            <v>40.662569809113911</v>
+            <v>39.557179787308016</v>
           </cell>
           <cell r="C30">
             <v>15</v>
           </cell>
           <cell r="D30">
-            <v>25.662569809113911</v>
+            <v>24.557179787308016</v>
           </cell>
         </row>
         <row r="32">
@@ -492,13 +492,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B34">
-            <v>91458.228558612973</v>
+            <v>71317.981957891461</v>
           </cell>
           <cell r="C34">
             <v>198171.9675</v>
           </cell>
           <cell r="D34">
-            <v>254046.48736557167</v>
+            <v>281341.62303068797</v>
           </cell>
         </row>
         <row r="35">
@@ -506,13 +506,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B35">
-            <v>298788.56295736902</v>
+            <v>290666.1570771393</v>
           </cell>
           <cell r="C35">
             <v>110743.91860786518</v>
           </cell>
           <cell r="D35">
-            <v>126113.30017915615</v>
+            <v>134235.70605938591</v>
           </cell>
         </row>
       </sheetData>
@@ -907,7 +907,7 @@
       </c>
       <c r="B5" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B5</f>
-        <v>321540</v>
+        <v>314158</v>
       </c>
       <c r="C5" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C5</f>
@@ -915,7 +915,7 @@
       </c>
       <c r="D5" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D5</f>
-        <v>43.758845944474686</v>
+        <v>42.754218835057159</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -952,7 +952,7 @@
       </c>
       <c r="B9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B9</f>
-        <v>91458.228558612973</v>
+        <v>71317.981957891461</v>
       </c>
       <c r="C9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C9</f>
@@ -960,7 +960,7 @@
       </c>
       <c r="D9" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D9</f>
-        <v>5.9749283699361708</v>
+        <v>4.6591743619188257</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -970,7 +970,7 @@
       </c>
       <c r="B10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B10</f>
-        <v>298788.56295736902</v>
+        <v>290666.1570771393</v>
       </c>
       <c r="C10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C10</f>
@@ -978,7 +978,7 @@
       </c>
       <c r="D10" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D10</f>
-        <v>40.662569809113911</v>
+        <v>39.557179787308016</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1082,11 +1082,11 @@
       </c>
       <c r="C19" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C19</f>
-        <v>475579.39212143701</v>
+        <v>468197.39212143701</v>
       </c>
       <c r="D19" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D19</f>
-        <v>0.32389837464215387</v>
+        <v>0.32900523307802532</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B20" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B20</f>
-        <v>321540</v>
+        <v>314158</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D20</f>
-        <v>0.67610162535784613</v>
+        <v>0.67099476692197468</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1138,15 +1138,15 @@
       </c>
       <c r="B24" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B24</f>
-        <v>91458.228558612973</v>
+        <v>71317.981957891461</v>
       </c>
       <c r="C24" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C24</f>
-        <v>390246.79151598201</v>
+        <v>361984.13903503073</v>
       </c>
       <c r="D24" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D24</f>
-        <v>0.23435997565368177</v>
+        <v>0.19701963226347252</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B25" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B25</f>
-        <v>298788.56295736902</v>
+        <v>290666.1570771393</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D25</f>
-        <v>0.76564002434631817</v>
+        <v>0.80298036773652759</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B29" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B29</f>
-        <v>5.9749283699361708</v>
+        <v>4.6591743619188257</v>
       </c>
       <c r="C29" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C29</f>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="D29" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D29</f>
-        <v>-4.0250716300638292</v>
+        <v>-5.3408256380811743</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B30" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B30</f>
-        <v>40.662569809113911</v>
+        <v>39.557179787308016</v>
       </c>
       <c r="C30" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C30</f>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="D30" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D30</f>
-        <v>25.662569809113911</v>
+        <v>24.557179787308016</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B34</f>
-        <v>91458.228558612973</v>
+        <v>71317.981957891461</v>
       </c>
       <c r="C34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C34</f>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="D34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D34</f>
-        <v>254046.48736557167</v>
+        <v>281341.62303068797</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="B35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B35</f>
-        <v>298788.56295736902</v>
+        <v>290666.1570771393</v>
       </c>
       <c r="C35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C35</f>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="D35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D35</f>
-        <v>126113.30017915615</v>
+        <v>134235.70605938591</v>
       </c>
     </row>
   </sheetData>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D06803-D9C6-4E8A-BE43-682447EA1831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CA9B2ED-5EEF-4086-922B-B19E23FB5C11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -263,13 +263,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B9">
-            <v>71317.981957891461</v>
+            <v>56923.932490944077</v>
           </cell>
           <cell r="C9">
             <v>15307</v>
           </cell>
           <cell r="D9">
-            <v>4.6591743619188257</v>
+            <v>3.7188170438978294</v>
           </cell>
         </row>
         <row r="10">
@@ -277,13 +277,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B10">
-            <v>290666.1570771393</v>
+            <v>292153.47485122917</v>
           </cell>
           <cell r="C10">
             <v>7348</v>
           </cell>
           <cell r="D10">
-            <v>39.557179787308016</v>
+            <v>39.759591024935922</v>
           </cell>
         </row>
         <row r="12">
@@ -310,13 +310,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B14">
-            <v>198171.9675</v>
+            <v>213982.5675</v>
           </cell>
           <cell r="C14">
             <v>344799.25199999998</v>
           </cell>
           <cell r="D14">
-            <v>0.57474593216344916</v>
+            <v>0.6206004399916738</v>
           </cell>
         </row>
         <row r="15">
@@ -401,13 +401,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B24">
-            <v>71317.981957891461</v>
+            <v>56923.932490944077</v>
           </cell>
           <cell r="C24">
-            <v>361984.13903503073</v>
+            <v>349077.40734217328</v>
           </cell>
           <cell r="D24">
-            <v>0.19701963226347252</v>
+            <v>0.1630696553075576</v>
           </cell>
         </row>
         <row r="25">
@@ -415,10 +415,10 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B25">
-            <v>290666.1570771393</v>
+            <v>292153.47485122917</v>
           </cell>
           <cell r="D25">
-            <v>0.80298036773652759</v>
+            <v>0.83693034469244232</v>
           </cell>
         </row>
         <row r="27">
@@ -445,13 +445,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B29">
-            <v>4.6591743619188257</v>
+            <v>3.7188170438978294</v>
           </cell>
           <cell r="C29">
             <v>10</v>
           </cell>
           <cell r="D29">
-            <v>-5.3408256380811743</v>
+            <v>-6.281182956102171</v>
           </cell>
         </row>
         <row r="30">
@@ -459,13 +459,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B30">
-            <v>39.557179787308016</v>
+            <v>39.759591024935922</v>
           </cell>
           <cell r="C30">
             <v>15</v>
           </cell>
           <cell r="D30">
-            <v>24.557179787308016</v>
+            <v>24.759591024935922</v>
           </cell>
         </row>
         <row r="32">
@@ -492,13 +492,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B34">
-            <v>71317.981957891461</v>
+            <v>56923.932490944077</v>
           </cell>
           <cell r="C34">
-            <v>198171.9675</v>
+            <v>213982.5675</v>
           </cell>
           <cell r="D34">
-            <v>281341.62303068797</v>
+            <v>295651.288518688</v>
           </cell>
         </row>
         <row r="35">
@@ -506,13 +506,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B35">
-            <v>290666.1570771393</v>
+            <v>292153.47485122917</v>
           </cell>
           <cell r="C35">
             <v>110743.91860786518</v>
           </cell>
           <cell r="D35">
-            <v>134235.70605938591</v>
+            <v>147798.84828529597</v>
           </cell>
         </row>
       </sheetData>
@@ -952,7 +952,7 @@
       </c>
       <c r="B9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B9</f>
-        <v>71317.981957891461</v>
+        <v>56923.932490944077</v>
       </c>
       <c r="C9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C9</f>
@@ -960,7 +960,7 @@
       </c>
       <c r="D9" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D9</f>
-        <v>4.6591743619188257</v>
+        <v>3.7188170438978294</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -970,7 +970,7 @@
       </c>
       <c r="B10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B10</f>
-        <v>290666.1570771393</v>
+        <v>292153.47485122917</v>
       </c>
       <c r="C10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C10</f>
@@ -978,7 +978,7 @@
       </c>
       <c r="D10" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D10</f>
-        <v>39.557179787308016</v>
+        <v>39.759591024935922</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B14</f>
-        <v>198171.9675</v>
+        <v>213982.5675</v>
       </c>
       <c r="C14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C14</f>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="D14" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D14</f>
-        <v>0.57474593216344916</v>
+        <v>0.6206004399916738</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1138,15 +1138,15 @@
       </c>
       <c r="B24" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B24</f>
-        <v>71317.981957891461</v>
+        <v>56923.932490944077</v>
       </c>
       <c r="C24" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C24</f>
-        <v>361984.13903503073</v>
+        <v>349077.40734217328</v>
       </c>
       <c r="D24" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D24</f>
-        <v>0.19701963226347252</v>
+        <v>0.1630696553075576</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B25" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B25</f>
-        <v>290666.1570771393</v>
+        <v>292153.47485122917</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D25</f>
-        <v>0.80298036773652759</v>
+        <v>0.83693034469244232</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B29" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B29</f>
-        <v>4.6591743619188257</v>
+        <v>3.7188170438978294</v>
       </c>
       <c r="C29" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C29</f>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="D29" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D29</f>
-        <v>-5.3408256380811743</v>
+        <v>-6.281182956102171</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B30" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B30</f>
-        <v>39.557179787308016</v>
+        <v>39.759591024935922</v>
       </c>
       <c r="C30" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C30</f>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="D30" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D30</f>
-        <v>24.557179787308016</v>
+        <v>24.759591024935922</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1261,15 +1261,15 @@
       </c>
       <c r="B34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B34</f>
-        <v>71317.981957891461</v>
+        <v>56923.932490944077</v>
       </c>
       <c r="C34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C34</f>
-        <v>198171.9675</v>
+        <v>213982.5675</v>
       </c>
       <c r="D34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D34</f>
-        <v>281341.62303068797</v>
+        <v>295651.288518688</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="B35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B35</f>
-        <v>290666.1570771393</v>
+        <v>292153.47485122917</v>
       </c>
       <c r="C35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C35</f>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="D35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D35</f>
-        <v>134235.70605938591</v>
+        <v>147798.84828529597</v>
       </c>
     </row>
   </sheetData>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CA9B2ED-5EEF-4086-922B-B19E23FB5C11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{157C2A42-1993-41A5-8375-86C29202DCA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -263,13 +263,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B9">
-            <v>56923.932490944077</v>
+            <v>121561.85262101516</v>
           </cell>
           <cell r="C9">
             <v>15307</v>
           </cell>
           <cell r="D9">
-            <v>3.7188170438978294</v>
+            <v>7.9415857203250253</v>
           </cell>
         </row>
         <row r="10">
@@ -277,13 +277,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B10">
-            <v>292153.47485122917</v>
+            <v>276001.54440655507</v>
           </cell>
           <cell r="C10">
             <v>7348</v>
           </cell>
           <cell r="D10">
-            <v>39.759591024935922</v>
+            <v>37.561451334588334</v>
           </cell>
         </row>
         <row r="12">
@@ -310,13 +310,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B14">
-            <v>213982.5675</v>
+            <v>285745.99550000002</v>
           </cell>
           <cell r="C14">
             <v>344799.25199999998</v>
           </cell>
           <cell r="D14">
-            <v>0.6206004399916738</v>
+            <v>0.82873148315298562</v>
           </cell>
         </row>
         <row r="15">
@@ -401,13 +401,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B24">
-            <v>56923.932490944077</v>
+            <v>121561.85262101516</v>
           </cell>
           <cell r="C24">
-            <v>349077.40734217328</v>
+            <v>397563.39702757023</v>
           </cell>
           <cell r="D24">
-            <v>0.1630696553075576</v>
+            <v>0.3057672148137548</v>
           </cell>
         </row>
         <row r="25">
@@ -415,10 +415,10 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B25">
-            <v>292153.47485122917</v>
+            <v>276001.54440655507</v>
           </cell>
           <cell r="D25">
-            <v>0.83693034469244232</v>
+            <v>0.6942327851862452</v>
           </cell>
         </row>
         <row r="27">
@@ -445,13 +445,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B29">
-            <v>3.7188170438978294</v>
+            <v>7.9415857203250253</v>
           </cell>
           <cell r="C29">
             <v>10</v>
           </cell>
           <cell r="D29">
-            <v>-6.281182956102171</v>
+            <v>-2.0584142796749747</v>
           </cell>
         </row>
         <row r="30">
@@ -459,13 +459,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B30">
-            <v>39.759591024935922</v>
+            <v>37.561451334588334</v>
           </cell>
           <cell r="C30">
             <v>15</v>
           </cell>
           <cell r="D30">
-            <v>24.759591024935922</v>
+            <v>22.561451334588334</v>
           </cell>
         </row>
         <row r="32">
@@ -492,13 +492,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B34">
-            <v>56923.932490944077</v>
+            <v>121561.85262101516</v>
           </cell>
           <cell r="C34">
-            <v>213982.5675</v>
+            <v>285745.99550000002</v>
           </cell>
           <cell r="D34">
-            <v>295651.288518688</v>
+            <v>317735.70971589047</v>
           </cell>
         </row>
         <row r="35">
@@ -506,13 +506,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B35">
-            <v>292153.47485122917</v>
+            <v>276001.54440655507</v>
           </cell>
           <cell r="C35">
             <v>110743.91860786518</v>
           </cell>
           <cell r="D35">
-            <v>147798.84828529597</v>
+            <v>157188.0149417659</v>
           </cell>
         </row>
       </sheetData>
@@ -952,7 +952,7 @@
       </c>
       <c r="B9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B9</f>
-        <v>56923.932490944077</v>
+        <v>121561.85262101516</v>
       </c>
       <c r="C9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C9</f>
@@ -960,7 +960,7 @@
       </c>
       <c r="D9" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D9</f>
-        <v>3.7188170438978294</v>
+        <v>7.9415857203250253</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -970,7 +970,7 @@
       </c>
       <c r="B10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B10</f>
-        <v>292153.47485122917</v>
+        <v>276001.54440655507</v>
       </c>
       <c r="C10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C10</f>
@@ -978,7 +978,7 @@
       </c>
       <c r="D10" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!D10</f>
-        <v>39.759591024935922</v>
+        <v>37.561451334588334</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B14</f>
-        <v>213982.5675</v>
+        <v>285745.99550000002</v>
       </c>
       <c r="C14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C14</f>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="D14" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D14</f>
-        <v>0.6206004399916738</v>
+        <v>0.82873148315298562</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1138,15 +1138,15 @@
       </c>
       <c r="B24" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B24</f>
-        <v>56923.932490944077</v>
+        <v>121561.85262101516</v>
       </c>
       <c r="C24" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C24</f>
-        <v>349077.40734217328</v>
+        <v>397563.39702757023</v>
       </c>
       <c r="D24" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D24</f>
-        <v>0.1630696553075576</v>
+        <v>0.3057672148137548</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B25" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B25</f>
-        <v>292153.47485122917</v>
+        <v>276001.54440655507</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D25</f>
-        <v>0.83693034469244232</v>
+        <v>0.6942327851862452</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B29" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B29</f>
-        <v>3.7188170438978294</v>
+        <v>7.9415857203250253</v>
       </c>
       <c r="C29" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C29</f>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="D29" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D29</f>
-        <v>-6.281182956102171</v>
+        <v>-2.0584142796749747</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B30" s="3">
         <f>'[1]DASHBOARD FINANCIERO'!B30</f>
-        <v>39.759591024935922</v>
+        <v>37.561451334588334</v>
       </c>
       <c r="C30" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C30</f>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="D30" s="6">
         <f>'[1]DASHBOARD FINANCIERO'!D30</f>
-        <v>24.759591024935922</v>
+        <v>22.561451334588334</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1261,15 +1261,15 @@
       </c>
       <c r="B34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B34</f>
-        <v>56923.932490944077</v>
+        <v>121561.85262101516</v>
       </c>
       <c r="C34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C34</f>
-        <v>213982.5675</v>
+        <v>285745.99550000002</v>
       </c>
       <c r="D34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D34</f>
-        <v>295651.288518688</v>
+        <v>317735.70971589047</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="B35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B35</f>
-        <v>292153.47485122917</v>
+        <v>276001.54440655507</v>
       </c>
       <c r="C35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C35</f>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="D35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D35</f>
-        <v>147798.84828529597</v>
+        <v>157188.0149417659</v>
       </c>
     </row>
   </sheetData>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{157C2A42-1993-41A5-8375-86C29202DCA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95FE6DFE-7653-4BA3-9A1A-BC5ACBF2A839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -219,10 +219,10 @@
             <v>154039.39212143701</v>
           </cell>
           <cell r="C4">
-            <v>15307</v>
+            <v>16722.932090310023</v>
           </cell>
           <cell r="D4">
-            <v>10.063329987681257</v>
+            <v>9.2112669769611735</v>
           </cell>
         </row>
         <row r="5">
@@ -233,10 +233,10 @@
             <v>314158</v>
           </cell>
           <cell r="C5">
-            <v>7348</v>
+            <v>8273.0534179876795</v>
           </cell>
           <cell r="D5">
-            <v>42.754218835057159</v>
+            <v>37.973645778346146</v>
           </cell>
         </row>
         <row r="7">
@@ -263,13 +263,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B9">
-            <v>121561.85262101516</v>
+            <v>122213.21077101516</v>
           </cell>
           <cell r="C9">
-            <v>15307</v>
+            <v>16722.932090310023</v>
           </cell>
           <cell r="D9">
-            <v>7.9415857203250253</v>
+            <v>7.3081209748995324</v>
           </cell>
         </row>
         <row r="10">
@@ -280,10 +280,10 @@
             <v>276001.54440655507</v>
           </cell>
           <cell r="C10">
-            <v>7348</v>
+            <v>8273.0534179876795</v>
           </cell>
           <cell r="D10">
-            <v>37.561451334588334</v>
+            <v>33.361508799938235</v>
           </cell>
         </row>
         <row r="12">
@@ -401,13 +401,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B24">
-            <v>121561.85262101516</v>
+            <v>122213.21077101516</v>
           </cell>
           <cell r="C24">
-            <v>397563.39702757023</v>
+            <v>398214.75517757022</v>
           </cell>
           <cell r="D24">
-            <v>0.3057672148137548</v>
+            <v>0.30690276837310654</v>
           </cell>
         </row>
         <row r="25">
@@ -418,7 +418,7 @@
             <v>276001.54440655507</v>
           </cell>
           <cell r="D25">
-            <v>0.6942327851862452</v>
+            <v>0.69309723162689352</v>
           </cell>
         </row>
         <row r="27">
@@ -445,13 +445,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B29">
-            <v>7.9415857203250253</v>
+            <v>7.3081209748995324</v>
           </cell>
           <cell r="C29">
             <v>10</v>
           </cell>
           <cell r="D29">
-            <v>-2.0584142796749747</v>
+            <v>-2.6918790251004676</v>
           </cell>
         </row>
         <row r="30">
@@ -459,13 +459,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B30">
-            <v>37.561451334588334</v>
+            <v>33.361508799938235</v>
           </cell>
           <cell r="C30">
             <v>15</v>
           </cell>
           <cell r="D30">
-            <v>22.561451334588334</v>
+            <v>18.361508799938235</v>
           </cell>
         </row>
         <row r="32">
@@ -492,7 +492,7 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B34">
-            <v>121561.85262101516</v>
+            <v>122213.21077101516</v>
           </cell>
           <cell r="C34">
             <v>285745.99550000002</v>
@@ -892,12 +892,12 @@
         <v>154039.39212143701</v>
       </c>
       <c r="C4" s="2">
-        <f>'[1]DASHBOARD FINANCIERO'!C4</f>
-        <v>15307</v>
+        <f ca="1">'[1]DASHBOARD FINANCIERO'!C4</f>
+        <v>16722.932090310023</v>
       </c>
       <c r="D4" s="3">
-        <f>'[1]DASHBOARD FINANCIERO'!D4</f>
-        <v>10.063329987681257</v>
+        <f ca="1">'[1]DASHBOARD FINANCIERO'!D4</f>
+        <v>9.2112669769611735</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -910,12 +910,12 @@
         <v>314158</v>
       </c>
       <c r="C5" s="2">
-        <f>'[1]DASHBOARD FINANCIERO'!C5</f>
-        <v>7348</v>
+        <f ca="1">'[1]DASHBOARD FINANCIERO'!C5</f>
+        <v>8273.0534179876795</v>
       </c>
       <c r="D5" s="3">
-        <f>'[1]DASHBOARD FINANCIERO'!D5</f>
-        <v>42.754218835057159</v>
+        <f ca="1">'[1]DASHBOARD FINANCIERO'!D5</f>
+        <v>37.973645778346146</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -952,15 +952,15 @@
       </c>
       <c r="B9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B9</f>
-        <v>121561.85262101516</v>
+        <v>122213.21077101516</v>
       </c>
       <c r="C9" s="2">
-        <f>'[1]DASHBOARD FINANCIERO'!C9</f>
-        <v>15307</v>
+        <f ca="1">'[1]DASHBOARD FINANCIERO'!C9</f>
+        <v>16722.932090310023</v>
       </c>
       <c r="D9" s="3">
-        <f>'[1]DASHBOARD FINANCIERO'!D9</f>
-        <v>7.9415857203250253</v>
+        <f ca="1">'[1]DASHBOARD FINANCIERO'!D9</f>
+        <v>7.3081209748995324</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -973,12 +973,12 @@
         <v>276001.54440655507</v>
       </c>
       <c r="C10" s="2">
-        <f>'[1]DASHBOARD FINANCIERO'!C10</f>
-        <v>7348</v>
+        <f ca="1">'[1]DASHBOARD FINANCIERO'!C10</f>
+        <v>8273.0534179876795</v>
       </c>
       <c r="D10" s="3">
-        <f>'[1]DASHBOARD FINANCIERO'!D10</f>
-        <v>37.561451334588334</v>
+        <f ca="1">'[1]DASHBOARD FINANCIERO'!D10</f>
+        <v>33.361508799938235</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1138,15 +1138,15 @@
       </c>
       <c r="B24" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B24</f>
-        <v>121561.85262101516</v>
+        <v>122213.21077101516</v>
       </c>
       <c r="C24" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C24</f>
-        <v>397563.39702757023</v>
+        <v>398214.75517757022</v>
       </c>
       <c r="D24" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D24</f>
-        <v>0.3057672148137548</v>
+        <v>0.30690276837310654</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1161,7 +1161,7 @@
       <c r="C25" s="9"/>
       <c r="D25" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D25</f>
-        <v>0.6942327851862452</v>
+        <v>0.69309723162689352</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1197,16 +1197,16 @@
         <v xml:space="preserve">MATERIA PRIMA </v>
       </c>
       <c r="B29" s="3">
-        <f>'[1]DASHBOARD FINANCIERO'!B29</f>
-        <v>7.9415857203250253</v>
+        <f ca="1">'[1]DASHBOARD FINANCIERO'!B29</f>
+        <v>7.3081209748995324</v>
       </c>
       <c r="C29" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C29</f>
         <v>10</v>
       </c>
       <c r="D29" s="6">
-        <f>'[1]DASHBOARD FINANCIERO'!D29</f>
-        <v>-2.0584142796749747</v>
+        <f ca="1">'[1]DASHBOARD FINANCIERO'!D29</f>
+        <v>-2.6918790251004676</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1215,16 +1215,16 @@
         <v>MATERIAL EMPAQUE</v>
       </c>
       <c r="B30" s="3">
-        <f>'[1]DASHBOARD FINANCIERO'!B30</f>
-        <v>37.561451334588334</v>
+        <f ca="1">'[1]DASHBOARD FINANCIERO'!B30</f>
+        <v>33.361508799938235</v>
       </c>
       <c r="C30" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C30</f>
         <v>15</v>
       </c>
       <c r="D30" s="6">
-        <f>'[1]DASHBOARD FINANCIERO'!D30</f>
-        <v>22.561451334588334</v>
+        <f ca="1">'[1]DASHBOARD FINANCIERO'!D30</f>
+        <v>18.361508799938235</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B34</f>
-        <v>121561.85262101516</v>
+        <v>122213.21077101516</v>
       </c>
       <c r="C34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C34</f>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95FE6DFE-7653-4BA3-9A1A-BC5ACBF2A839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F2C2951-EF1B-4396-99BD-35376C86F80D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -218,9 +218,6 @@
           <cell r="B4">
             <v>154039.39212143701</v>
           </cell>
-          <cell r="C4">
-            <v>16722.932090310023</v>
-          </cell>
           <cell r="D4">
             <v>9.2112669769611735</v>
           </cell>
@@ -232,9 +229,6 @@
           <cell r="B5">
             <v>314158</v>
           </cell>
-          <cell r="C5">
-            <v>8273.0534179876795</v>
-          </cell>
           <cell r="D5">
             <v>37.973645778346146</v>
           </cell>
@@ -265,9 +259,6 @@
           <cell r="B9">
             <v>122213.21077101516</v>
           </cell>
-          <cell r="C9">
-            <v>16722.932090310023</v>
-          </cell>
           <cell r="D9">
             <v>7.3081209748995324</v>
           </cell>
@@ -278,9 +269,6 @@
           </cell>
           <cell r="B10">
             <v>276001.54440655507</v>
-          </cell>
-          <cell r="C10">
-            <v>8273.0534179876795</v>
           </cell>
           <cell r="D10">
             <v>33.361508799938235</v>
@@ -892,7 +880,6 @@
         <v>154039.39212143701</v>
       </c>
       <c r="C4" s="2">
-        <f ca="1">'[1]DASHBOARD FINANCIERO'!C4</f>
         <v>16722.932090310023</v>
       </c>
       <c r="D4" s="3">
@@ -910,7 +897,6 @@
         <v>314158</v>
       </c>
       <c r="C5" s="2">
-        <f ca="1">'[1]DASHBOARD FINANCIERO'!C5</f>
         <v>8273.0534179876795</v>
       </c>
       <c r="D5" s="3">
@@ -955,7 +941,6 @@
         <v>122213.21077101516</v>
       </c>
       <c r="C9" s="2">
-        <f ca="1">'[1]DASHBOARD FINANCIERO'!C9</f>
         <v>16722.932090310023</v>
       </c>
       <c r="D9" s="3">
@@ -973,7 +958,6 @@
         <v>276001.54440655507</v>
       </c>
       <c r="C10" s="2">
-        <f ca="1">'[1]DASHBOARD FINANCIERO'!C10</f>
         <v>8273.0534179876795</v>
       </c>
       <c r="D10" s="3">

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F2C2951-EF1B-4396-99BD-35376C86F80D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23ED8033-4223-4DEB-AD28-DA5727975BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23ED8033-4223-4DEB-AD28-DA5727975BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9737407-1B3B-46A3-8FB1-64F333AD18F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -219,7 +219,7 @@
             <v>154039.39212143701</v>
           </cell>
           <cell r="D4">
-            <v>9.2112669769611735</v>
+            <v>9.0888549278404138</v>
           </cell>
         </row>
         <row r="5">
@@ -230,7 +230,7 @@
             <v>314158</v>
           </cell>
           <cell r="D5">
-            <v>37.973645778346146</v>
+            <v>37.876822471413604</v>
           </cell>
         </row>
         <row r="7">
@@ -257,10 +257,10 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B9">
-            <v>122213.21077101516</v>
+            <v>103456.26381861775</v>
           </cell>
           <cell r="D9">
-            <v>7.3081209748995324</v>
+            <v>6.1042760574030099</v>
           </cell>
         </row>
         <row r="10">
@@ -268,10 +268,10 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B10">
-            <v>276001.54440655507</v>
+            <v>287499.54992385278</v>
           </cell>
           <cell r="D10">
-            <v>33.361508799938235</v>
+            <v>34.662715617864528</v>
           </cell>
         </row>
         <row r="12">
@@ -298,13 +298,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B14">
-            <v>285745.99550000002</v>
+            <v>286025.41850000003</v>
           </cell>
           <cell r="C14">
             <v>344799.25199999998</v>
           </cell>
           <cell r="D14">
-            <v>0.82873148315298562</v>
+            <v>0.82954187644235389</v>
           </cell>
         </row>
         <row r="15">
@@ -312,13 +312,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B15">
-            <v>110743.91860786518</v>
+            <v>130935.38607942848</v>
           </cell>
           <cell r="C15">
             <v>108924.24443806437</v>
           </cell>
           <cell r="D15">
-            <v>1.0167058691036917</v>
+            <v>1.2020775241996735</v>
           </cell>
         </row>
         <row r="17">
@@ -389,13 +389,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B24">
-            <v>122213.21077101516</v>
+            <v>103456.26381861775</v>
           </cell>
           <cell r="C24">
-            <v>398214.75517757022</v>
+            <v>390955.81374247052</v>
           </cell>
           <cell r="D24">
-            <v>0.30690276837310654</v>
+            <v>0.26462392982027944</v>
           </cell>
         </row>
         <row r="25">
@@ -403,10 +403,10 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B25">
-            <v>276001.54440655507</v>
+            <v>287499.54992385278</v>
           </cell>
           <cell r="D25">
-            <v>0.69309723162689352</v>
+            <v>0.73537607017972062</v>
           </cell>
         </row>
         <row r="27">
@@ -433,13 +433,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B29">
-            <v>7.3081209748995324</v>
+            <v>6.1042760574030099</v>
           </cell>
           <cell r="C29">
             <v>10</v>
           </cell>
           <cell r="D29">
-            <v>-2.6918790251004676</v>
+            <v>-3.8957239425969901</v>
           </cell>
         </row>
         <row r="30">
@@ -447,13 +447,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B30">
-            <v>33.361508799938235</v>
+            <v>34.662715617864528</v>
           </cell>
           <cell r="C30">
             <v>15</v>
           </cell>
           <cell r="D30">
-            <v>18.361508799938235</v>
+            <v>19.662715617864528</v>
           </cell>
         </row>
         <row r="32">
@@ -480,13 +480,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B34">
-            <v>122213.21077101516</v>
+            <v>103456.26381861775</v>
           </cell>
           <cell r="C34">
-            <v>285745.99550000002</v>
+            <v>286025.41850000003</v>
           </cell>
           <cell r="D34">
-            <v>317735.70971589047</v>
+            <v>338963.25410496577</v>
           </cell>
         </row>
         <row r="35">
@@ -494,13 +494,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B35">
-            <v>276001.54440655507</v>
+            <v>287499.54992385278</v>
           </cell>
           <cell r="C35">
-            <v>110743.91860786518</v>
+            <v>130935.38607942848</v>
           </cell>
           <cell r="D35">
-            <v>157188.0149417659</v>
+            <v>165884.03118403151</v>
           </cell>
         </row>
       </sheetData>
@@ -884,7 +884,7 @@
       </c>
       <c r="D4" s="3">
         <f ca="1">'[1]DASHBOARD FINANCIERO'!D4</f>
-        <v>9.2112669769611735</v>
+        <v>9.0888549278404138</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -901,7 +901,7 @@
       </c>
       <c r="D5" s="3">
         <f ca="1">'[1]DASHBOARD FINANCIERO'!D5</f>
-        <v>37.973645778346146</v>
+        <v>37.876822471413604</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -938,14 +938,14 @@
       </c>
       <c r="B9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B9</f>
-        <v>122213.21077101516</v>
+        <v>103456.26381861775</v>
       </c>
       <c r="C9" s="2">
         <v>16722.932090310023</v>
       </c>
       <c r="D9" s="3">
         <f ca="1">'[1]DASHBOARD FINANCIERO'!D9</f>
-        <v>7.3081209748995324</v>
+        <v>6.1042760574030099</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -955,14 +955,14 @@
       </c>
       <c r="B10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B10</f>
-        <v>276001.54440655507</v>
+        <v>287499.54992385278</v>
       </c>
       <c r="C10" s="2">
         <v>8273.0534179876795</v>
       </c>
       <c r="D10" s="3">
         <f ca="1">'[1]DASHBOARD FINANCIERO'!D10</f>
-        <v>33.361508799938235</v>
+        <v>34.662715617864528</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -999,7 +999,7 @@
       </c>
       <c r="B14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B14</f>
-        <v>285745.99550000002</v>
+        <v>286025.41850000003</v>
       </c>
       <c r="C14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C14</f>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="D14" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D14</f>
-        <v>0.82873148315298562</v>
+        <v>0.82954187644235389</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="B15" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B15</f>
-        <v>110743.91860786518</v>
+        <v>130935.38607942848</v>
       </c>
       <c r="C15" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C15</f>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="D15" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D15</f>
-        <v>1.0167058691036917</v>
+        <v>1.2020775241996735</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1122,15 +1122,15 @@
       </c>
       <c r="B24" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B24</f>
-        <v>122213.21077101516</v>
+        <v>103456.26381861775</v>
       </c>
       <c r="C24" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C24</f>
-        <v>398214.75517757022</v>
+        <v>390955.81374247052</v>
       </c>
       <c r="D24" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D24</f>
-        <v>0.30690276837310654</v>
+        <v>0.26462392982027944</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B25" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B25</f>
-        <v>276001.54440655507</v>
+        <v>287499.54992385278</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D25</f>
-        <v>0.69309723162689352</v>
+        <v>0.73537607017972062</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="B29" s="3">
         <f ca="1">'[1]DASHBOARD FINANCIERO'!B29</f>
-        <v>7.3081209748995324</v>
+        <v>6.1042760574030099</v>
       </c>
       <c r="C29" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C29</f>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="D29" s="6">
         <f ca="1">'[1]DASHBOARD FINANCIERO'!D29</f>
-        <v>-2.6918790251004676</v>
+        <v>-3.8957239425969901</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="B30" s="3">
         <f ca="1">'[1]DASHBOARD FINANCIERO'!B30</f>
-        <v>33.361508799938235</v>
+        <v>34.662715617864528</v>
       </c>
       <c r="C30" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C30</f>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="D30" s="6">
         <f ca="1">'[1]DASHBOARD FINANCIERO'!D30</f>
-        <v>18.361508799938235</v>
+        <v>19.662715617864528</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1245,15 +1245,15 @@
       </c>
       <c r="B34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B34</f>
-        <v>122213.21077101516</v>
+        <v>103456.26381861775</v>
       </c>
       <c r="C34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C34</f>
-        <v>285745.99550000002</v>
+        <v>286025.41850000003</v>
       </c>
       <c r="D34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D34</f>
-        <v>317735.70971589047</v>
+        <v>338963.25410496577</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1263,15 +1263,15 @@
       </c>
       <c r="B35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B35</f>
-        <v>276001.54440655507</v>
+        <v>287499.54992385278</v>
       </c>
       <c r="C35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C35</f>
-        <v>110743.91860786518</v>
+        <v>130935.38607942848</v>
       </c>
       <c r="D35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D35</f>
-        <v>157188.0149417659</v>
+        <v>165884.03118403151</v>
       </c>
     </row>
   </sheetData>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9737407-1B3B-46A3-8FB1-64F333AD18F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{456F2F8C-524B-428E-A8A5-9E900C7FBE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -219,7 +219,7 @@
             <v>154039.39212143701</v>
           </cell>
           <cell r="D4">
-            <v>9.0888549278404138</v>
+            <v>9.3177637014384711</v>
           </cell>
         </row>
         <row r="5">
@@ -230,7 +230,7 @@
             <v>314158</v>
           </cell>
           <cell r="D5">
-            <v>37.876822471413604</v>
+            <v>37.918002788221209</v>
           </cell>
         </row>
         <row r="7">
@@ -257,10 +257,10 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B9">
-            <v>103456.26381861775</v>
+            <v>96280.685511117772</v>
           </cell>
           <cell r="D9">
-            <v>6.1042760574030099</v>
+            <v>5.8239692084597472</v>
           </cell>
         </row>
         <row r="10">
@@ -268,10 +268,10 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B10">
-            <v>287499.54992385278</v>
+            <v>287083.56319918693</v>
           </cell>
           <cell r="D10">
-            <v>34.662715617864528</v>
+            <v>34.650193055211865</v>
           </cell>
         </row>
         <row r="12">
@@ -312,13 +312,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B15">
-            <v>130935.38607942848</v>
+            <v>138624.32007942849</v>
           </cell>
           <cell r="C15">
             <v>108924.24443806437</v>
           </cell>
           <cell r="D15">
-            <v>1.2020775241996735</v>
+            <v>1.2726672633313691</v>
           </cell>
         </row>
         <row r="17">
@@ -389,13 +389,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B24">
-            <v>103456.26381861775</v>
+            <v>96280.685511117772</v>
           </cell>
           <cell r="C24">
-            <v>390955.81374247052</v>
+            <v>383364.24871030473</v>
           </cell>
           <cell r="D24">
-            <v>0.26462392982027944</v>
+            <v>0.25114675099470163</v>
           </cell>
         </row>
         <row r="25">
@@ -403,10 +403,10 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B25">
-            <v>287499.54992385278</v>
+            <v>287083.56319918693</v>
           </cell>
           <cell r="D25">
-            <v>0.73537607017972062</v>
+            <v>0.74885324900529826</v>
           </cell>
         </row>
         <row r="27">
@@ -433,13 +433,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B29">
-            <v>6.1042760574030099</v>
+            <v>5.8239692084597472</v>
           </cell>
           <cell r="C29">
             <v>10</v>
           </cell>
           <cell r="D29">
-            <v>-3.8957239425969901</v>
+            <v>-4.1760307915402528</v>
           </cell>
         </row>
         <row r="30">
@@ -447,13 +447,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B30">
-            <v>34.662715617864528</v>
+            <v>34.650193055211865</v>
           </cell>
           <cell r="C30">
             <v>15</v>
           </cell>
           <cell r="D30">
-            <v>19.662715617864528</v>
+            <v>19.650193055211865</v>
           </cell>
         </row>
         <row r="32">
@@ -480,13 +480,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B34">
-            <v>103456.26381861775</v>
+            <v>96280.685511117772</v>
           </cell>
           <cell r="C34">
             <v>286025.41850000003</v>
           </cell>
           <cell r="D34">
-            <v>338963.25410496577</v>
+            <v>347167.76881246583</v>
           </cell>
         </row>
         <row r="35">
@@ -494,13 +494,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B35">
-            <v>287499.54992385278</v>
+            <v>287083.56319918693</v>
           </cell>
           <cell r="C35">
-            <v>130935.38607942848</v>
+            <v>138624.32007942849</v>
           </cell>
           <cell r="D35">
-            <v>165884.03118403151</v>
+            <v>173989.0689086974</v>
           </cell>
         </row>
       </sheetData>
@@ -884,7 +884,7 @@
       </c>
       <c r="D4" s="3">
         <f ca="1">'[1]DASHBOARD FINANCIERO'!D4</f>
-        <v>9.0888549278404138</v>
+        <v>9.3177637014384711</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -901,7 +901,7 @@
       </c>
       <c r="D5" s="3">
         <f ca="1">'[1]DASHBOARD FINANCIERO'!D5</f>
-        <v>37.876822471413604</v>
+        <v>37.918002788221209</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -938,14 +938,14 @@
       </c>
       <c r="B9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B9</f>
-        <v>103456.26381861775</v>
+        <v>96280.685511117772</v>
       </c>
       <c r="C9" s="2">
         <v>16722.932090310023</v>
       </c>
       <c r="D9" s="3">
         <f ca="1">'[1]DASHBOARD FINANCIERO'!D9</f>
-        <v>6.1042760574030099</v>
+        <v>5.8239692084597472</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -955,14 +955,14 @@
       </c>
       <c r="B10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B10</f>
-        <v>287499.54992385278</v>
+        <v>287083.56319918693</v>
       </c>
       <c r="C10" s="2">
         <v>8273.0534179876795</v>
       </c>
       <c r="D10" s="3">
         <f ca="1">'[1]DASHBOARD FINANCIERO'!D10</f>
-        <v>34.662715617864528</v>
+        <v>34.650193055211865</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="B15" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B15</f>
-        <v>130935.38607942848</v>
+        <v>138624.32007942849</v>
       </c>
       <c r="C15" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C15</f>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="D15" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D15</f>
-        <v>1.2020775241996735</v>
+        <v>1.2726672633313691</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1122,15 +1122,15 @@
       </c>
       <c r="B24" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B24</f>
-        <v>103456.26381861775</v>
+        <v>96280.685511117772</v>
       </c>
       <c r="C24" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C24</f>
-        <v>390955.81374247052</v>
+        <v>383364.24871030473</v>
       </c>
       <c r="D24" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D24</f>
-        <v>0.26462392982027944</v>
+        <v>0.25114675099470163</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B25" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B25</f>
-        <v>287499.54992385278</v>
+        <v>287083.56319918693</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D25</f>
-        <v>0.73537607017972062</v>
+        <v>0.74885324900529826</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="B29" s="3">
         <f ca="1">'[1]DASHBOARD FINANCIERO'!B29</f>
-        <v>6.1042760574030099</v>
+        <v>5.8239692084597472</v>
       </c>
       <c r="C29" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C29</f>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="D29" s="6">
         <f ca="1">'[1]DASHBOARD FINANCIERO'!D29</f>
-        <v>-3.8957239425969901</v>
+        <v>-4.1760307915402528</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="B30" s="3">
         <f ca="1">'[1]DASHBOARD FINANCIERO'!B30</f>
-        <v>34.662715617864528</v>
+        <v>34.650193055211865</v>
       </c>
       <c r="C30" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C30</f>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="D30" s="6">
         <f ca="1">'[1]DASHBOARD FINANCIERO'!D30</f>
-        <v>19.662715617864528</v>
+        <v>19.650193055211865</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="B34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B34</f>
-        <v>103456.26381861775</v>
+        <v>96280.685511117772</v>
       </c>
       <c r="C34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C34</f>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="D34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D34</f>
-        <v>338963.25410496577</v>
+        <v>347167.76881246583</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1263,15 +1263,15 @@
       </c>
       <c r="B35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B35</f>
-        <v>287499.54992385278</v>
+        <v>287083.56319918693</v>
       </c>
       <c r="C35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C35</f>
-        <v>130935.38607942848</v>
+        <v>138624.32007942849</v>
       </c>
       <c r="D35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D35</f>
-        <v>165884.03118403151</v>
+        <v>173989.0689086974</v>
       </c>
     </row>
   </sheetData>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{456F2F8C-524B-428E-A8A5-9E900C7FBE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83A250A-4285-47D7-888B-F09EB7BF66B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
@@ -34,6 +34,14 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+  <si>
+    <t>DASHBOARD - FINANCIERO - KPIs</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -168,11 +176,11 @@
       <sheetName val="MPS"/>
       <sheetName val="BOM (Recetas)"/>
       <sheetName val="Explosión de materiales"/>
-      <sheetName val="FOTORequerimienMateriaPrima09"/>
+      <sheetName val="FOTORequerimienMateriaPrima10"/>
       <sheetName val="Requerimiento Materia Prima"/>
       <sheetName val="VINCULO MP"/>
       <sheetName val="VALOR $ CONSUMO MP"/>
-      <sheetName val="FOTORequerimienMaterialConten09"/>
+      <sheetName val="FOTORequerimienMaterialConten10"/>
       <sheetName val="Requerimien Material Contenedor"/>
       <sheetName val="VINCULO MC"/>
       <sheetName val="VALOR $ CONSUMO MC"/>
@@ -187,11 +195,6 @@
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1">
-        <row r="1">
-          <cell r="A1" t="str">
-            <v>DASHBOARD - FINANCIERO - KPIs - SEPTIEMBRE 2026</v>
-          </cell>
-        </row>
         <row r="2">
           <cell r="A2" t="str">
             <v>DIAS DE COBERTURA (INICIO MES)</v>
@@ -216,10 +219,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B4">
-            <v>154039.39212143701</v>
+            <v>98512</v>
+          </cell>
+          <cell r="C4">
+            <v>16308.416113180272</v>
           </cell>
           <cell r="D4">
-            <v>9.3177637014384711</v>
+            <v>6.0405620825669111</v>
           </cell>
         </row>
         <row r="5">
@@ -227,10 +233,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B5">
-            <v>314158</v>
+            <v>279710</v>
+          </cell>
+          <cell r="C5">
+            <v>8213.3775174174825</v>
           </cell>
           <cell r="D5">
-            <v>37.918002788221209</v>
+            <v>34.055417446335611</v>
           </cell>
         </row>
         <row r="7">
@@ -257,10 +266,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B9">
-            <v>96280.685511117772</v>
+            <v>99438.311812585423</v>
+          </cell>
+          <cell r="C9">
+            <v>16308.416113180272</v>
           </cell>
           <cell r="D9">
-            <v>5.8239692084597472</v>
+            <v>6.0973617010066681</v>
           </cell>
         </row>
         <row r="10">
@@ -268,10 +280,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B10">
-            <v>287083.56319918693</v>
+            <v>258536.65860655956</v>
+          </cell>
+          <cell r="C10">
+            <v>8213.3775174174825</v>
           </cell>
           <cell r="D10">
-            <v>34.650193055211865</v>
+            <v>31.477508255075406</v>
           </cell>
         </row>
         <row r="12">
@@ -298,13 +313,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B14">
-            <v>286025.41850000003</v>
+            <v>0</v>
           </cell>
           <cell r="C14">
-            <v>344799.25199999998</v>
+            <v>403455.17050000001</v>
           </cell>
           <cell r="D14">
-            <v>0.82954187644235389</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="15">
@@ -312,13 +327,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B15">
-            <v>138624.32007942849</v>
+            <v>0</v>
           </cell>
           <cell r="C15">
-            <v>108924.24443806437</v>
+            <v>93998.107645677228</v>
           </cell>
           <cell r="D15">
-            <v>1.2726672633313691</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="17">
@@ -345,13 +360,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B19">
-            <v>154039.39212143701</v>
+            <v>98512</v>
           </cell>
           <cell r="C19">
-            <v>468197.39212143701</v>
+            <v>378222</v>
           </cell>
           <cell r="D19">
-            <v>0.32900523307802532</v>
+            <v>0.26046078757978119</v>
           </cell>
         </row>
         <row r="20">
@@ -359,10 +374,10 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B20">
-            <v>314158</v>
+            <v>279710</v>
           </cell>
           <cell r="D20">
-            <v>0.67099476692197468</v>
+            <v>0.73953921242021881</v>
           </cell>
         </row>
         <row r="22">
@@ -389,13 +404,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B24">
-            <v>96280.685511117772</v>
+            <v>99438.311812585423</v>
           </cell>
           <cell r="C24">
-            <v>383364.24871030473</v>
+            <v>357974.97041914496</v>
           </cell>
           <cell r="D24">
-            <v>0.25114675099470163</v>
+            <v>0.27778006852310178</v>
           </cell>
         </row>
         <row r="25">
@@ -403,10 +418,10 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B25">
-            <v>287083.56319918693</v>
+            <v>258536.65860655956</v>
           </cell>
           <cell r="D25">
-            <v>0.74885324900529826</v>
+            <v>0.72221993147689834</v>
           </cell>
         </row>
         <row r="27">
@@ -433,13 +448,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B29">
-            <v>5.8239692084597472</v>
+            <v>6.0973617010066681</v>
           </cell>
           <cell r="C29">
             <v>10</v>
           </cell>
           <cell r="D29">
-            <v>-4.1760307915402528</v>
+            <v>-3.9026382989933319</v>
           </cell>
         </row>
         <row r="30">
@@ -447,13 +462,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B30">
-            <v>34.650193055211865</v>
+            <v>31.477508255075406</v>
           </cell>
           <cell r="C30">
             <v>15</v>
           </cell>
           <cell r="D30">
-            <v>19.650193055211865</v>
+            <v>16.477508255075406</v>
           </cell>
         </row>
         <row r="32">
@@ -480,13 +495,13 @@
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
           <cell r="B34">
-            <v>96280.685511117772</v>
+            <v>99438.311812585423</v>
           </cell>
           <cell r="C34">
-            <v>286025.41850000003</v>
+            <v>0</v>
           </cell>
           <cell r="D34">
-            <v>347167.76881246583</v>
+            <v>222.51444228875584</v>
           </cell>
         </row>
         <row r="35">
@@ -494,13 +509,13 @@
             <v>MATERIAL EMPAQUE</v>
           </cell>
           <cell r="B35">
-            <v>287083.56319918693</v>
+            <v>258536.65860655956</v>
           </cell>
           <cell r="C35">
-            <v>138624.32007942849</v>
+            <v>0</v>
           </cell>
           <cell r="D35">
-            <v>173989.0689086974</v>
+            <v>2437.0753660138203</v>
           </cell>
         </row>
       </sheetData>
@@ -835,9 +850,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="str">
-        <f>'[1]DASHBOARD FINANCIERO'!A1</f>
-        <v>DASHBOARD - FINANCIERO - KPIs - SEPTIEMBRE 2026</v>
+      <c r="A1" s="10" t="s">
+        <v>0</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -877,14 +891,15 @@
       </c>
       <c r="B4" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B4</f>
-        <v>154039.39212143701</v>
+        <v>98512</v>
       </c>
       <c r="C4" s="2">
-        <v>16722.932090310023</v>
+        <f>'[1]DASHBOARD FINANCIERO'!C4</f>
+        <v>16308.416113180272</v>
       </c>
       <c r="D4" s="3">
-        <f ca="1">'[1]DASHBOARD FINANCIERO'!D4</f>
-        <v>9.3177637014384711</v>
+        <f>'[1]DASHBOARD FINANCIERO'!D4</f>
+        <v>6.0405620825669111</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -894,14 +909,15 @@
       </c>
       <c r="B5" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B5</f>
-        <v>314158</v>
+        <v>279710</v>
       </c>
       <c r="C5" s="2">
-        <v>8273.0534179876795</v>
+        <f>'[1]DASHBOARD FINANCIERO'!C5</f>
+        <v>8213.3775174174825</v>
       </c>
       <c r="D5" s="3">
-        <f ca="1">'[1]DASHBOARD FINANCIERO'!D5</f>
-        <v>37.918002788221209</v>
+        <f>'[1]DASHBOARD FINANCIERO'!D5</f>
+        <v>34.055417446335611</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -938,14 +954,15 @@
       </c>
       <c r="B9" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B9</f>
-        <v>96280.685511117772</v>
+        <v>99438.311812585423</v>
       </c>
       <c r="C9" s="2">
-        <v>16722.932090310023</v>
+        <f>'[1]DASHBOARD FINANCIERO'!C9</f>
+        <v>16308.416113180272</v>
       </c>
       <c r="D9" s="3">
-        <f ca="1">'[1]DASHBOARD FINANCIERO'!D9</f>
-        <v>5.8239692084597472</v>
+        <f>'[1]DASHBOARD FINANCIERO'!D9</f>
+        <v>6.0973617010066681</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -955,14 +972,15 @@
       </c>
       <c r="B10" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B10</f>
-        <v>287083.56319918693</v>
+        <v>258536.65860655956</v>
       </c>
       <c r="C10" s="2">
-        <v>8273.0534179876795</v>
+        <f>'[1]DASHBOARD FINANCIERO'!C10</f>
+        <v>8213.3775174174825</v>
       </c>
       <c r="D10" s="3">
-        <f ca="1">'[1]DASHBOARD FINANCIERO'!D10</f>
-        <v>34.650193055211865</v>
+        <f>'[1]DASHBOARD FINANCIERO'!D10</f>
+        <v>31.477508255075406</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -999,15 +1017,15 @@
       </c>
       <c r="B14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B14</f>
-        <v>286025.41850000003</v>
+        <v>0</v>
       </c>
       <c r="C14" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C14</f>
-        <v>344799.25199999998</v>
+        <v>403455.17050000001</v>
       </c>
       <c r="D14" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D14</f>
-        <v>0.82954187644235389</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1017,15 +1035,15 @@
       </c>
       <c r="B15" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B15</f>
-        <v>138624.32007942849</v>
+        <v>0</v>
       </c>
       <c r="C15" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C15</f>
-        <v>108924.24443806437</v>
+        <v>93998.107645677228</v>
       </c>
       <c r="D15" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D15</f>
-        <v>1.2726672633313691</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1062,15 +1080,15 @@
       </c>
       <c r="B19" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B19</f>
-        <v>154039.39212143701</v>
+        <v>98512</v>
       </c>
       <c r="C19" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C19</f>
-        <v>468197.39212143701</v>
+        <v>378222</v>
       </c>
       <c r="D19" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D19</f>
-        <v>0.32900523307802532</v>
+        <v>0.26046078757978119</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1080,12 +1098,12 @@
       </c>
       <c r="B20" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B20</f>
-        <v>314158</v>
+        <v>279710</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D20</f>
-        <v>0.67099476692197468</v>
+        <v>0.73953921242021881</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1122,15 +1140,15 @@
       </c>
       <c r="B24" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B24</f>
-        <v>96280.685511117772</v>
+        <v>99438.311812585423</v>
       </c>
       <c r="C24" s="9">
         <f>'[1]DASHBOARD FINANCIERO'!C24</f>
-        <v>383364.24871030473</v>
+        <v>357974.97041914496</v>
       </c>
       <c r="D24" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D24</f>
-        <v>0.25114675099470163</v>
+        <v>0.27778006852310178</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1140,12 +1158,12 @@
       </c>
       <c r="B25" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B25</f>
-        <v>287083.56319918693</v>
+        <v>258536.65860655956</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="4">
         <f>'[1]DASHBOARD FINANCIERO'!D25</f>
-        <v>0.74885324900529826</v>
+        <v>0.72221993147689834</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1181,16 +1199,16 @@
         <v xml:space="preserve">MATERIA PRIMA </v>
       </c>
       <c r="B29" s="3">
-        <f ca="1">'[1]DASHBOARD FINANCIERO'!B29</f>
-        <v>5.8239692084597472</v>
+        <f>'[1]DASHBOARD FINANCIERO'!B29</f>
+        <v>6.0973617010066681</v>
       </c>
       <c r="C29" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C29</f>
         <v>10</v>
       </c>
       <c r="D29" s="6">
-        <f ca="1">'[1]DASHBOARD FINANCIERO'!D29</f>
-        <v>-4.1760307915402528</v>
+        <f>'[1]DASHBOARD FINANCIERO'!D29</f>
+        <v>-3.9026382989933319</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1199,16 +1217,16 @@
         <v>MATERIAL EMPAQUE</v>
       </c>
       <c r="B30" s="3">
-        <f ca="1">'[1]DASHBOARD FINANCIERO'!B30</f>
-        <v>34.650193055211865</v>
+        <f>'[1]DASHBOARD FINANCIERO'!B30</f>
+        <v>31.477508255075406</v>
       </c>
       <c r="C30" s="7">
         <f>'[1]DASHBOARD FINANCIERO'!C30</f>
         <v>15</v>
       </c>
       <c r="D30" s="6">
-        <f ca="1">'[1]DASHBOARD FINANCIERO'!D30</f>
-        <v>19.650193055211865</v>
+        <f>'[1]DASHBOARD FINANCIERO'!D30</f>
+        <v>16.477508255075406</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1245,15 +1263,15 @@
       </c>
       <c r="B34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B34</f>
-        <v>96280.685511117772</v>
+        <v>99438.311812585423</v>
       </c>
       <c r="C34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C34</f>
-        <v>286025.41850000003</v>
+        <v>0</v>
       </c>
       <c r="D34" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D34</f>
-        <v>347167.76881246583</v>
+        <v>222.51444228875584</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1263,15 +1281,15 @@
       </c>
       <c r="B35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!B35</f>
-        <v>287083.56319918693</v>
+        <v>258536.65860655956</v>
       </c>
       <c r="C35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!C35</f>
-        <v>138624.32007942849</v>
+        <v>0</v>
       </c>
       <c r="D35" s="2">
         <f>'[1]DASHBOARD FINANCIERO'!D35</f>
-        <v>173989.0689086974</v>
+        <v>2437.0753660138203</v>
       </c>
     </row>
   </sheetData>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -2,23 +2,24 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr updateLinks="always" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\SUPPLY CHAIN\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83A250A-4285-47D7-888B-F09EB7BF66B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30FD7B55-F23A-4FE3-B833-51FB1E8B840E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -166,7 +167,6 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="REQUERIMIENTO COMPRAS"/>
@@ -218,29 +218,11 @@
           <cell r="A4" t="str">
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
-          <cell r="B4">
-            <v>98512</v>
-          </cell>
-          <cell r="C4">
-            <v>16308.416113180272</v>
-          </cell>
-          <cell r="D4">
-            <v>6.0405620825669111</v>
-          </cell>
         </row>
         <row r="5">
           <cell r="A5" t="str">
             <v>MATERIAL EMPAQUE</v>
           </cell>
-          <cell r="B5">
-            <v>279710</v>
-          </cell>
-          <cell r="C5">
-            <v>8213.3775174174825</v>
-          </cell>
-          <cell r="D5">
-            <v>34.055417446335611</v>
-          </cell>
         </row>
         <row r="7">
           <cell r="A7" t="str">
@@ -265,29 +247,11 @@
           <cell r="A9" t="str">
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
-          <cell r="B9">
-            <v>99438.311812585423</v>
-          </cell>
-          <cell r="C9">
-            <v>16308.416113180272</v>
-          </cell>
-          <cell r="D9">
-            <v>6.0973617010066681</v>
-          </cell>
         </row>
         <row r="10">
           <cell r="A10" t="str">
             <v>MATERIAL EMPAQUE</v>
           </cell>
-          <cell r="B10">
-            <v>258536.65860655956</v>
-          </cell>
-          <cell r="C10">
-            <v>8213.3775174174825</v>
-          </cell>
-          <cell r="D10">
-            <v>31.477508255075406</v>
-          </cell>
         </row>
         <row r="12">
           <cell r="A12" t="str">
@@ -312,29 +276,11 @@
           <cell r="A14" t="str">
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
-          <cell r="B14">
-            <v>0</v>
-          </cell>
-          <cell r="C14">
-            <v>403455.17050000001</v>
-          </cell>
-          <cell r="D14">
-            <v>0</v>
-          </cell>
         </row>
         <row r="15">
           <cell r="A15" t="str">
             <v>MATERIAL EMPAQUE</v>
           </cell>
-          <cell r="B15">
-            <v>0</v>
-          </cell>
-          <cell r="C15">
-            <v>93998.107645677228</v>
-          </cell>
-          <cell r="D15">
-            <v>0</v>
-          </cell>
         </row>
         <row r="17">
           <cell r="A17" t="str">
@@ -359,26 +305,11 @@
           <cell r="A19" t="str">
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
-          <cell r="B19">
-            <v>98512</v>
-          </cell>
-          <cell r="C19">
-            <v>378222</v>
-          </cell>
-          <cell r="D19">
-            <v>0.26046078757978119</v>
-          </cell>
         </row>
         <row r="20">
           <cell r="A20" t="str">
             <v>MATERIAL EMPAQUE</v>
           </cell>
-          <cell r="B20">
-            <v>279710</v>
-          </cell>
-          <cell r="D20">
-            <v>0.73953921242021881</v>
-          </cell>
         </row>
         <row r="22">
           <cell r="A22" t="str">
@@ -403,26 +334,11 @@
           <cell r="A24" t="str">
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
-          <cell r="B24">
-            <v>99438.311812585423</v>
-          </cell>
-          <cell r="C24">
-            <v>357974.97041914496</v>
-          </cell>
-          <cell r="D24">
-            <v>0.27778006852310178</v>
-          </cell>
         </row>
         <row r="25">
           <cell r="A25" t="str">
             <v>MATERIAL EMPAQUE</v>
           </cell>
-          <cell r="B25">
-            <v>258536.65860655956</v>
-          </cell>
-          <cell r="D25">
-            <v>0.72221993147689834</v>
-          </cell>
         </row>
         <row r="27">
           <cell r="A27" t="str">
@@ -447,29 +363,11 @@
           <cell r="A29" t="str">
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
-          <cell r="B29">
-            <v>6.0973617010066681</v>
-          </cell>
-          <cell r="C29">
-            <v>10</v>
-          </cell>
-          <cell r="D29">
-            <v>-3.9026382989933319</v>
-          </cell>
         </row>
         <row r="30">
           <cell r="A30" t="str">
             <v>MATERIAL EMPAQUE</v>
           </cell>
-          <cell r="B30">
-            <v>31.477508255075406</v>
-          </cell>
-          <cell r="C30">
-            <v>15</v>
-          </cell>
-          <cell r="D30">
-            <v>16.477508255075406</v>
-          </cell>
         </row>
         <row r="32">
           <cell r="A32" t="str">
@@ -494,28 +392,218 @@
           <cell r="A34" t="str">
             <v xml:space="preserve">MATERIA PRIMA </v>
           </cell>
-          <cell r="B34">
-            <v>99438.311812585423</v>
-          </cell>
-          <cell r="C34">
-            <v>0</v>
-          </cell>
-          <cell r="D34">
-            <v>222.51444228875584</v>
-          </cell>
         </row>
         <row r="35">
           <cell r="A35" t="str">
             <v>MATERIAL EMPAQUE</v>
           </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="REQUERIMIENTO COMPRAS"/>
+      <sheetName val="DASHBOARD FINANCIERO"/>
+      <sheetName val="VINCULO VTS BY SKU"/>
+      <sheetName val="FILL RATE"/>
+      <sheetName val="MPS"/>
+      <sheetName val="BOM (Recetas)"/>
+      <sheetName val="Explosión de materiales"/>
+      <sheetName val="FOTORequerimienMateriaPrima10"/>
+      <sheetName val="Requerimiento Materia Prima"/>
+      <sheetName val="VINCULO MP"/>
+      <sheetName val="VALOR $ CONSUMO MP"/>
+      <sheetName val="FOTORequerimienMaterialConten10"/>
+      <sheetName val="Requerimien Material Contenedor"/>
+      <sheetName val="VINCULO MC"/>
+      <sheetName val="VALOR $ CONSUMO MC"/>
+      <sheetName val="FOTORequerimientoMaterialEmpa09"/>
+      <sheetName val="Requerimiento Material Empaque"/>
+      <sheetName val="VINCULO ME"/>
+      <sheetName val="VALOR $ CONSUMO ME"/>
+      <sheetName val="Plan Producción Semanal"/>
+      <sheetName val="Plan Maduraciòn Semanal"/>
+      <sheetName val="Panel Producción Diario"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="4">
+          <cell r="B4">
+            <v>98512</v>
+          </cell>
+          <cell r="C4">
+            <v>16308.416113180272</v>
+          </cell>
+          <cell r="D4">
+            <v>6.0405620825669111</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="B5">
+            <v>279710</v>
+          </cell>
+          <cell r="C5">
+            <v>8213.3775174174825</v>
+          </cell>
+          <cell r="D5">
+            <v>34.055417446335611</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="B9">
+            <v>182726.29840555659</v>
+          </cell>
+          <cell r="C9">
+            <v>16308.416113180272</v>
+          </cell>
+          <cell r="D9">
+            <v>11.204417224667166</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="B10">
+            <v>260804.22592608465</v>
+          </cell>
+          <cell r="C10">
+            <v>8213.3775174174825</v>
+          </cell>
+          <cell r="D10">
+            <v>31.75359045325958</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="B14">
+            <v>127312.37800000001</v>
+          </cell>
+          <cell r="C14">
+            <v>403455.17050000001</v>
+          </cell>
+          <cell r="D14">
+            <v>0.31555520243357499</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="B15">
+            <v>6892.1362332197787</v>
+          </cell>
+          <cell r="C15">
+            <v>93998.107645677228</v>
+          </cell>
+          <cell r="D15">
+            <v>7.3322074303872789E-2</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="B19">
+            <v>98512</v>
+          </cell>
+          <cell r="C19">
+            <v>378222</v>
+          </cell>
+          <cell r="D19">
+            <v>0.26046078757978119</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="B20">
+            <v>279710</v>
+          </cell>
+          <cell r="D20">
+            <v>0.73953921242021881</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="B24">
+            <v>182726.29840555659</v>
+          </cell>
+          <cell r="C24">
+            <v>443530.52433164127</v>
+          </cell>
+          <cell r="D24">
+            <v>0.41198133697992467</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="B25">
+            <v>260804.22592608465</v>
+          </cell>
+          <cell r="D25">
+            <v>0.58801866302007522</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="B29">
+            <v>11.204417224667166</v>
+          </cell>
+          <cell r="C29">
+            <v>10</v>
+          </cell>
+          <cell r="D29">
+            <v>1.2044172246671661</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="B30">
+            <v>31.75359045325958</v>
+          </cell>
+          <cell r="C30">
+            <v>15</v>
+          </cell>
+          <cell r="D30">
+            <v>16.75359045325958</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="B34">
+            <v>182726.29840555659</v>
+          </cell>
+          <cell r="C34">
+            <v>127312.37800000001</v>
+          </cell>
+          <cell r="D34">
+            <v>22043.04880002814</v>
+          </cell>
+        </row>
+        <row r="35">
           <cell r="B35">
-            <v>258536.65860655956</v>
+            <v>260804.22592608465</v>
           </cell>
           <cell r="C35">
-            <v>0</v>
+            <v>6892.1362332197787</v>
           </cell>
           <cell r="D35">
-            <v>2437.0753660138203</v>
+            <v>11737.412743182771</v>
           </cell>
         </row>
       </sheetData>
@@ -842,14 +930,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BCBA687-646F-4D57-AB43-78E40D81A358}">
   <dimension ref="A1:D35"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.42578125" customWidth="1"/>
-    <col min="2" max="2" width="29.28515625" customWidth="1"/>
-    <col min="3" max="4" width="27.5703125" customWidth="1"/>
+    <col min="1" max="1" width="23.44140625" customWidth="1"/>
+    <col min="2" max="2" width="29.33203125" customWidth="1"/>
+    <col min="3" max="4" width="27.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -857,7 +945,7 @@
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
     </row>
-    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A2</f>
         <v>DIAS DE COBERTURA (INICIO MES)</v>
@@ -866,7 +954,7 @@
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A3</f>
         <v>CATEGORIA</v>
@@ -884,43 +972,43 @@
         <v>DIAS DE COBERTURA (DIO)</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A4</f>
         <v xml:space="preserve">MATERIA PRIMA </v>
       </c>
       <c r="B4" s="2">
-        <f>'[1]DASHBOARD FINANCIERO'!B4</f>
+        <f>'[2]DASHBOARD FINANCIERO'!B4</f>
         <v>98512</v>
       </c>
       <c r="C4" s="2">
-        <f>'[1]DASHBOARD FINANCIERO'!C4</f>
+        <f>'[2]DASHBOARD FINANCIERO'!C4</f>
         <v>16308.416113180272</v>
       </c>
       <c r="D4" s="3">
-        <f>'[1]DASHBOARD FINANCIERO'!D4</f>
+        <f>'[2]DASHBOARD FINANCIERO'!D4</f>
         <v>6.0405620825669111</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A5</f>
         <v>MATERIAL EMPAQUE</v>
       </c>
       <c r="B5" s="2">
-        <f>'[1]DASHBOARD FINANCIERO'!B5</f>
+        <f>'[2]DASHBOARD FINANCIERO'!B5</f>
         <v>279710</v>
       </c>
       <c r="C5" s="2">
-        <f>'[1]DASHBOARD FINANCIERO'!C5</f>
+        <f>'[2]DASHBOARD FINANCIERO'!C5</f>
         <v>8213.3775174174825</v>
       </c>
       <c r="D5" s="3">
-        <f>'[1]DASHBOARD FINANCIERO'!D5</f>
+        <f>'[2]DASHBOARD FINANCIERO'!D5</f>
         <v>34.055417446335611</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A7</f>
         <v>DIAS DE COBERTURA (TIEMPO REAL)</v>
@@ -929,7 +1017,7 @@
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A8</f>
         <v>CATEGORIA</v>
@@ -947,43 +1035,43 @@
         <v>DIAS DE COBERTURA (DIO)</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A9</f>
         <v xml:space="preserve">MATERIA PRIMA </v>
       </c>
       <c r="B9" s="2">
-        <f>'[1]DASHBOARD FINANCIERO'!B9</f>
-        <v>99438.311812585423</v>
+        <f>'[2]DASHBOARD FINANCIERO'!B9</f>
+        <v>182726.29840555659</v>
       </c>
       <c r="C9" s="2">
-        <f>'[1]DASHBOARD FINANCIERO'!C9</f>
+        <f>'[2]DASHBOARD FINANCIERO'!C9</f>
         <v>16308.416113180272</v>
       </c>
       <c r="D9" s="3">
-        <f>'[1]DASHBOARD FINANCIERO'!D9</f>
-        <v>6.0973617010066681</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <f>'[2]DASHBOARD FINANCIERO'!D9</f>
+        <v>11.204417224667166</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A10</f>
         <v>MATERIAL EMPAQUE</v>
       </c>
       <c r="B10" s="2">
-        <f>'[1]DASHBOARD FINANCIERO'!B10</f>
-        <v>258536.65860655956</v>
+        <f>'[2]DASHBOARD FINANCIERO'!B10</f>
+        <v>260804.22592608465</v>
       </c>
       <c r="C10" s="2">
-        <f>'[1]DASHBOARD FINANCIERO'!C10</f>
+        <f>'[2]DASHBOARD FINANCIERO'!C10</f>
         <v>8213.3775174174825</v>
       </c>
       <c r="D10" s="3">
-        <f>'[1]DASHBOARD FINANCIERO'!D10</f>
-        <v>31.477508255075406</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <f>'[2]DASHBOARD FINANCIERO'!D10</f>
+        <v>31.75359045325958</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A12</f>
         <v>SUPPLIER FILL RATE</v>
@@ -992,7 +1080,7 @@
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A13</f>
         <v>CATEGORIA</v>
@@ -1010,43 +1098,43 @@
         <v>FILL RATE</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A14</f>
         <v xml:space="preserve">MATERIA PRIMA </v>
       </c>
       <c r="B14" s="2">
-        <f>'[1]DASHBOARD FINANCIERO'!B14</f>
-        <v>0</v>
+        <f>'[2]DASHBOARD FINANCIERO'!B14</f>
+        <v>127312.37800000001</v>
       </c>
       <c r="C14" s="2">
-        <f>'[1]DASHBOARD FINANCIERO'!C14</f>
+        <f>'[2]DASHBOARD FINANCIERO'!C14</f>
         <v>403455.17050000001</v>
       </c>
       <c r="D14" s="4">
-        <f>'[1]DASHBOARD FINANCIERO'!D14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <f>'[2]DASHBOARD FINANCIERO'!D14</f>
+        <v>0.31555520243357499</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A15</f>
         <v>MATERIAL EMPAQUE</v>
       </c>
       <c r="B15" s="2">
-        <f>'[1]DASHBOARD FINANCIERO'!B15</f>
-        <v>0</v>
+        <f>'[2]DASHBOARD FINANCIERO'!B15</f>
+        <v>6892.1362332197787</v>
       </c>
       <c r="C15" s="2">
-        <f>'[1]DASHBOARD FINANCIERO'!C15</f>
+        <f>'[2]DASHBOARD FINANCIERO'!C15</f>
         <v>93998.107645677228</v>
       </c>
       <c r="D15" s="4">
-        <f>'[1]DASHBOARD FINANCIERO'!D15</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <f>'[2]DASHBOARD FINANCIERO'!D15</f>
+        <v>7.3322074303872789E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A17</f>
         <v>ESTRUCTURA DEL CAPITAL INMOVILIZADO (INICIO MES)</v>
@@ -1055,7 +1143,7 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A18</f>
         <v>CATEGORIA</v>
@@ -1073,40 +1161,40 @@
         <v>CAPITAL ALLOCATION</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A19</f>
         <v xml:space="preserve">MATERIA PRIMA </v>
       </c>
       <c r="B19" s="2">
-        <f>'[1]DASHBOARD FINANCIERO'!B19</f>
+        <f>'[2]DASHBOARD FINANCIERO'!B19</f>
         <v>98512</v>
       </c>
       <c r="C19" s="9">
-        <f>'[1]DASHBOARD FINANCIERO'!C19</f>
+        <f>'[2]DASHBOARD FINANCIERO'!C19</f>
         <v>378222</v>
       </c>
       <c r="D19" s="4">
-        <f>'[1]DASHBOARD FINANCIERO'!D19</f>
+        <f>'[2]DASHBOARD FINANCIERO'!D19</f>
         <v>0.26046078757978119</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A20</f>
         <v>MATERIAL EMPAQUE</v>
       </c>
       <c r="B20" s="2">
-        <f>'[1]DASHBOARD FINANCIERO'!B20</f>
+        <f>'[2]DASHBOARD FINANCIERO'!B20</f>
         <v>279710</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="4">
-        <f>'[1]DASHBOARD FINANCIERO'!D20</f>
+        <f>'[2]DASHBOARD FINANCIERO'!D20</f>
         <v>0.73953921242021881</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A22</f>
         <v>ESTRUCTURA DEL CAPITAL INMOVILIZADO (TIEMPO REAL)</v>
@@ -1115,7 +1203,7 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A23</f>
         <v>CATEGORIA</v>
@@ -1133,40 +1221,40 @@
         <v>CAPITAL ALLOCATION</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A24</f>
         <v xml:space="preserve">MATERIA PRIMA </v>
       </c>
       <c r="B24" s="2">
-        <f>'[1]DASHBOARD FINANCIERO'!B24</f>
-        <v>99438.311812585423</v>
+        <f>'[2]DASHBOARD FINANCIERO'!B24</f>
+        <v>182726.29840555659</v>
       </c>
       <c r="C24" s="9">
-        <f>'[1]DASHBOARD FINANCIERO'!C24</f>
-        <v>357974.97041914496</v>
+        <f>'[2]DASHBOARD FINANCIERO'!C24</f>
+        <v>443530.52433164127</v>
       </c>
       <c r="D24" s="4">
-        <f>'[1]DASHBOARD FINANCIERO'!D24</f>
-        <v>0.27778006852310178</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+        <f>'[2]DASHBOARD FINANCIERO'!D24</f>
+        <v>0.41198133697992467</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A25</f>
         <v>MATERIAL EMPAQUE</v>
       </c>
       <c r="B25" s="2">
-        <f>'[1]DASHBOARD FINANCIERO'!B25</f>
-        <v>258536.65860655956</v>
+        <f>'[2]DASHBOARD FINANCIERO'!B25</f>
+        <v>260804.22592608465</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="4">
-        <f>'[1]DASHBOARD FINANCIERO'!D25</f>
-        <v>0.72221993147689834</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <f>'[2]DASHBOARD FINANCIERO'!D25</f>
+        <v>0.58801866302007522</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A27</f>
         <v>VARIABLE DE TIEMPO DE ENTREGA</v>
@@ -1175,7 +1263,7 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A28</f>
         <v>CATEGORIA</v>
@@ -1193,43 +1281,43 @@
         <v>MARGEN DE SEGURIDAD</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A29</f>
         <v xml:space="preserve">MATERIA PRIMA </v>
       </c>
       <c r="B29" s="3">
-        <f>'[1]DASHBOARD FINANCIERO'!B29</f>
-        <v>6.0973617010066681</v>
+        <f>'[2]DASHBOARD FINANCIERO'!B29</f>
+        <v>11.204417224667166</v>
       </c>
       <c r="C29" s="7">
-        <f>'[1]DASHBOARD FINANCIERO'!C29</f>
+        <f>'[2]DASHBOARD FINANCIERO'!C29</f>
         <v>10</v>
       </c>
       <c r="D29" s="6">
-        <f>'[1]DASHBOARD FINANCIERO'!D29</f>
-        <v>-3.9026382989933319</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+        <f>'[2]DASHBOARD FINANCIERO'!D29</f>
+        <v>1.2044172246671661</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A30</f>
         <v>MATERIAL EMPAQUE</v>
       </c>
       <c r="B30" s="3">
-        <f>'[1]DASHBOARD FINANCIERO'!B30</f>
-        <v>31.477508255075406</v>
+        <f>'[2]DASHBOARD FINANCIERO'!B30</f>
+        <v>31.75359045325958</v>
       </c>
       <c r="C30" s="7">
-        <f>'[1]DASHBOARD FINANCIERO'!C30</f>
+        <f>'[2]DASHBOARD FINANCIERO'!C30</f>
         <v>15</v>
       </c>
       <c r="D30" s="6">
-        <f>'[1]DASHBOARD FINANCIERO'!D30</f>
-        <v>16.477508255075406</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <f>'[2]DASHBOARD FINANCIERO'!D30</f>
+        <v>16.75359045325958</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A32</f>
         <v>MOVIMIENTOS (MES ACTUAL)</v>
@@ -1238,7 +1326,7 @@
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A33</f>
         <v>CATEGORIA</v>
@@ -1256,40 +1344,40 @@
         <v>CONSUMO (USD)</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A34</f>
         <v xml:space="preserve">MATERIA PRIMA </v>
       </c>
       <c r="B34" s="2">
-        <f>'[1]DASHBOARD FINANCIERO'!B34</f>
-        <v>99438.311812585423</v>
+        <f>'[2]DASHBOARD FINANCIERO'!B34</f>
+        <v>182726.29840555659</v>
       </c>
       <c r="C34" s="2">
-        <f>'[1]DASHBOARD FINANCIERO'!C34</f>
-        <v>0</v>
+        <f>'[2]DASHBOARD FINANCIERO'!C34</f>
+        <v>127312.37800000001</v>
       </c>
       <c r="D34" s="2">
-        <f>'[1]DASHBOARD FINANCIERO'!D34</f>
-        <v>222.51444228875584</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+        <f>'[2]DASHBOARD FINANCIERO'!D34</f>
+        <v>22043.04880002814</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A35</f>
         <v>MATERIAL EMPAQUE</v>
       </c>
       <c r="B35" s="2">
-        <f>'[1]DASHBOARD FINANCIERO'!B35</f>
-        <v>258536.65860655956</v>
+        <f>'[2]DASHBOARD FINANCIERO'!B35</f>
+        <v>260804.22592608465</v>
       </c>
       <c r="C35" s="2">
-        <f>'[1]DASHBOARD FINANCIERO'!C35</f>
-        <v>0</v>
+        <f>'[2]DASHBOARD FINANCIERO'!C35</f>
+        <v>6892.1362332197787</v>
       </c>
       <c r="D35" s="2">
-        <f>'[1]DASHBOARD FINANCIERO'!D35</f>
-        <v>2437.0753660138203</v>
+        <f>'[2]DASHBOARD FINANCIERO'!D35</f>
+        <v>11737.412743182771</v>
       </c>
     </row>
   </sheetData>

--- a/data/Kpis Financieros Inventario.xlsx
+++ b/data/Kpis Financieros Inventario.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\SUPPLY CHAIN\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30FD7B55-F23A-4FE3-B833-51FB1E8B840E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE709BB-A006-41BE-8FCD-425DD4E62EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{438CA555-B5FD-48EA-A9D0-CDEF222AFC24}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
     <externalReference r:id="rId3"/>
   </externalReferences>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -482,35 +482,35 @@
         </row>
         <row r="9">
           <cell r="B9">
-            <v>182726.29840555659</v>
+            <v>148747.56501353366</v>
           </cell>
           <cell r="C9">
             <v>16308.416113180272</v>
           </cell>
           <cell r="D9">
-            <v>11.204417224667166</v>
+            <v>9.1209081238316951</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>260804.22592608465</v>
+            <v>235917.84893290888</v>
           </cell>
           <cell r="C10">
             <v>8213.3775174174825</v>
           </cell>
           <cell r="D10">
-            <v>31.75359045325958</v>
+            <v>28.723609554366142</v>
           </cell>
         </row>
         <row r="14">
           <cell r="B14">
-            <v>127312.37800000001</v>
+            <v>153982.22400000002</v>
           </cell>
           <cell r="C14">
             <v>403455.17050000001</v>
           </cell>
           <cell r="D14">
-            <v>0.31555520243357499</v>
+            <v>0.38165881926651379</v>
           </cell>
         </row>
         <row r="15">
@@ -545,65 +545,65 @@
         </row>
         <row r="24">
           <cell r="B24">
-            <v>182726.29840555659</v>
+            <v>148747.56501353366</v>
           </cell>
           <cell r="C24">
-            <v>443530.52433164127</v>
+            <v>384665.41394644254</v>
           </cell>
           <cell r="D24">
-            <v>0.41198133697992467</v>
+            <v>0.38669336940763793</v>
           </cell>
         </row>
         <row r="25">
           <cell r="B25">
-            <v>260804.22592608465</v>
+            <v>235917.84893290888</v>
           </cell>
           <cell r="D25">
-            <v>0.58801866302007522</v>
+            <v>0.61330663059236212</v>
           </cell>
         </row>
         <row r="29">
           <cell r="B29">
-            <v>11.204417224667166</v>
+            <v>9.1209081238316951</v>
           </cell>
           <cell r="C29">
             <v>10</v>
           </cell>
           <cell r="D29">
-            <v>1.2044172246671661</v>
+            <v>-0.87909187616830486</v>
           </cell>
         </row>
         <row r="30">
           <cell r="B30">
-            <v>31.75359045325958</v>
+            <v>28.723609554366142</v>
           </cell>
           <cell r="C30">
             <v>15</v>
           </cell>
           <cell r="D30">
-            <v>16.75359045325958</v>
+            <v>13.723609554366142</v>
           </cell>
         </row>
         <row r="34">
           <cell r="B34">
-            <v>182726.29840555659</v>
+            <v>148747.56501353366</v>
           </cell>
           <cell r="C34">
-            <v>127312.37800000001</v>
+            <v>153982.22400000002</v>
           </cell>
           <cell r="D34">
-            <v>22043.04880002814</v>
+            <v>90536.571390355675</v>
           </cell>
         </row>
         <row r="35">
           <cell r="B35">
-            <v>260804.22592608465</v>
+            <v>235917.84893290888</v>
           </cell>
           <cell r="C35">
             <v>6892.1362332197787</v>
           </cell>
           <cell r="D35">
-            <v>11737.412743182771</v>
+            <v>36852.447472619227</v>
           </cell>
         </row>
       </sheetData>
@@ -930,14 +930,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BCBA687-646F-4D57-AB43-78E40D81A358}">
   <dimension ref="A1:D35"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.44140625" customWidth="1"/>
-    <col min="2" max="2" width="29.33203125" customWidth="1"/>
-    <col min="3" max="4" width="27.5546875" customWidth="1"/>
+    <col min="1" max="1" width="23.42578125" customWidth="1"/>
+    <col min="2" max="2" width="29.28515625" customWidth="1"/>
+    <col min="3" max="4" width="27.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -945,7 +945,7 @@
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
     </row>
-    <row r="2" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A2</f>
         <v>DIAS DE COBERTURA (INICIO MES)</v>
@@ -954,7 +954,7 @@
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A3</f>
         <v>CATEGORIA</v>
@@ -972,7 +972,7 @@
         <v>DIAS DE COBERTURA (DIO)</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A4</f>
         <v xml:space="preserve">MATERIA PRIMA </v>
@@ -990,7 +990,7 @@
         <v>6.0405620825669111</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A5</f>
         <v>MATERIAL EMPAQUE</v>
@@ -1008,7 +1008,7 @@
         <v>34.055417446335611</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A7</f>
         <v>DIAS DE COBERTURA (TIEMPO REAL)</v>
@@ -1017,7 +1017,7 @@
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A8</f>
         <v>CATEGORIA</v>
@@ -1035,14 +1035,14 @@
         <v>DIAS DE COBERTURA (DIO)</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A9</f>
         <v xml:space="preserve">MATERIA PRIMA </v>
       </c>
       <c r="B9" s="2">
         <f>'[2]DASHBOARD FINANCIERO'!B9</f>
-        <v>182726.29840555659</v>
+        <v>148747.56501353366</v>
       </c>
       <c r="C9" s="2">
         <f>'[2]DASHBOARD FINANCIERO'!C9</f>
@@ -1050,17 +1050,17 @@
       </c>
       <c r="D9" s="3">
         <f>'[2]DASHBOARD FINANCIERO'!D9</f>
-        <v>11.204417224667166</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>9.1209081238316951</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A10</f>
         <v>MATERIAL EMPAQUE</v>
       </c>
       <c r="B10" s="2">
         <f>'[2]DASHBOARD FINANCIERO'!B10</f>
-        <v>260804.22592608465</v>
+        <v>235917.84893290888</v>
       </c>
       <c r="C10" s="2">
         <f>'[2]DASHBOARD FINANCIERO'!C10</f>
@@ -1068,10 +1068,10 @@
       </c>
       <c r="D10" s="3">
         <f>'[2]DASHBOARD FINANCIERO'!D10</f>
-        <v>31.75359045325958</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>28.723609554366142</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A12</f>
         <v>SUPPLIER FILL RATE</v>
@@ -1080,7 +1080,7 @@
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A13</f>
         <v>CATEGORIA</v>
@@ -1098,14 +1098,14 @@
         <v>FILL RATE</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A14</f>
         <v xml:space="preserve">MATERIA PRIMA </v>
       </c>
       <c r="B14" s="2">
         <f>'[2]DASHBOARD FINANCIERO'!B14</f>
-        <v>127312.37800000001</v>
+        <v>153982.22400000002</v>
       </c>
       <c r="C14" s="2">
         <f>'[2]DASHBOARD FINANCIERO'!C14</f>
@@ -1113,10 +1113,10 @@
       </c>
       <c r="D14" s="4">
         <f>'[2]DASHBOARD FINANCIERO'!D14</f>
-        <v>0.31555520243357499</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0.38165881926651379</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A15</f>
         <v>MATERIAL EMPAQUE</v>
@@ -1134,7 +1134,7 @@
         <v>7.3322074303872789E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A17</f>
         <v>ESTRUCTURA DEL CAPITAL INMOVILIZADO (INICIO MES)</v>
@@ -1143,7 +1143,7 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A18</f>
         <v>CATEGORIA</v>
@@ -1161,7 +1161,7 @@
         <v>CAPITAL ALLOCATION</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A19</f>
         <v xml:space="preserve">MATERIA PRIMA </v>
@@ -1179,7 +1179,7 @@
         <v>0.26046078757978119</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A20</f>
         <v>MATERIAL EMPAQUE</v>
@@ -1194,7 +1194,7 @@
         <v>0.73953921242021881</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A22</f>
         <v>ESTRUCTURA DEL CAPITAL INMOVILIZADO (TIEMPO REAL)</v>
@@ -1203,7 +1203,7 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A23</f>
         <v>CATEGORIA</v>
@@ -1221,40 +1221,40 @@
         <v>CAPITAL ALLOCATION</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A24</f>
         <v xml:space="preserve">MATERIA PRIMA </v>
       </c>
       <c r="B24" s="2">
         <f>'[2]DASHBOARD FINANCIERO'!B24</f>
-        <v>182726.29840555659</v>
+        <v>148747.56501353366</v>
       </c>
       <c r="C24" s="9">
         <f>'[2]DASHBOARD FINANCIERO'!C24</f>
-        <v>443530.52433164127</v>
+        <v>384665.41394644254</v>
       </c>
       <c r="D24" s="4">
         <f>'[2]DASHBOARD FINANCIERO'!D24</f>
-        <v>0.41198133697992467</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0.38669336940763793</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A25</f>
         <v>MATERIAL EMPAQUE</v>
       </c>
       <c r="B25" s="2">
         <f>'[2]DASHBOARD FINANCIERO'!B25</f>
-        <v>260804.22592608465</v>
+        <v>235917.84893290888</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="4">
         <f>'[2]DASHBOARD FINANCIERO'!D25</f>
-        <v>0.58801866302007522</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>0.61330663059236212</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A27</f>
         <v>VARIABLE DE TIEMPO DE ENTREGA</v>
@@ -1263,7 +1263,7 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A28</f>
         <v>CATEGORIA</v>
@@ -1281,14 +1281,14 @@
         <v>MARGEN DE SEGURIDAD</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A29</f>
         <v xml:space="preserve">MATERIA PRIMA </v>
       </c>
       <c r="B29" s="3">
         <f>'[2]DASHBOARD FINANCIERO'!B29</f>
-        <v>11.204417224667166</v>
+        <v>9.1209081238316951</v>
       </c>
       <c r="C29" s="7">
         <f>'[2]DASHBOARD FINANCIERO'!C29</f>
@@ -1296,17 +1296,17 @@
       </c>
       <c r="D29" s="6">
         <f>'[2]DASHBOARD FINANCIERO'!D29</f>
-        <v>1.2044172246671661</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+        <v>-0.87909187616830486</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A30</f>
         <v>MATERIAL EMPAQUE</v>
       </c>
       <c r="B30" s="3">
         <f>'[2]DASHBOARD FINANCIERO'!B30</f>
-        <v>31.75359045325958</v>
+        <v>28.723609554366142</v>
       </c>
       <c r="C30" s="7">
         <f>'[2]DASHBOARD FINANCIERO'!C30</f>
@@ -1314,10 +1314,10 @@
       </c>
       <c r="D30" s="6">
         <f>'[2]DASHBOARD FINANCIERO'!D30</f>
-        <v>16.75359045325958</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>13.723609554366142</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A32</f>
         <v>MOVIMIENTOS (MES ACTUAL)</v>
@@ -1326,7 +1326,7 @@
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A33</f>
         <v>CATEGORIA</v>
@@ -1344,32 +1344,32 @@
         <v>CONSUMO (USD)</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A34</f>
         <v xml:space="preserve">MATERIA PRIMA </v>
       </c>
       <c r="B34" s="2">
         <f>'[2]DASHBOARD FINANCIERO'!B34</f>
-        <v>182726.29840555659</v>
+        <v>148747.56501353366</v>
       </c>
       <c r="C34" s="2">
         <f>'[2]DASHBOARD FINANCIERO'!C34</f>
-        <v>127312.37800000001</v>
+        <v>153982.22400000002</v>
       </c>
       <c r="D34" s="2">
         <f>'[2]DASHBOARD FINANCIERO'!D34</f>
-        <v>22043.04880002814</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+        <v>90536.571390355675</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="str">
         <f>'[1]DASHBOARD FINANCIERO'!A35</f>
         <v>MATERIAL EMPAQUE</v>
       </c>
       <c r="B35" s="2">
         <f>'[2]DASHBOARD FINANCIERO'!B35</f>
-        <v>260804.22592608465</v>
+        <v>235917.84893290888</v>
       </c>
       <c r="C35" s="2">
         <f>'[2]DASHBOARD FINANCIERO'!C35</f>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="D35" s="2">
         <f>'[2]DASHBOARD FINANCIERO'!D35</f>
-        <v>11737.412743182771</v>
+        <v>36852.447472619227</v>
       </c>
     </row>
   </sheetData>
